--- a/data-engineering/docs/review-table-20261024/sample.xlsx
+++ b/data-engineering/docs/review-table-20261024/sample.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="抽样30道" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="抽样核对" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -448,14 +448,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>这 30 道菜按固定种子 20261024 抽自“复核表里的值被导入的菜”，按导入的餐型角色分层。</t>
+          <t>这些菜按固定种子 20261024 抽自这一批。一部分的值来自你的复核表（AI 预填、在聊天里按菜品类型确认，</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>导入值来自你的复核表，是 AI 预填、在聊天里按菜品类型确认的，没有人逐条看过食材，所以现在仍记为 AI 估计、未复核。</t>
+          <t>没有人逐条看过食材），另一部分的值是现行规则给的。两部分现在都记为未复核；表里不标来源，请一律独立判断。</t>
         </is>
       </c>
     </row>
@@ -479,42 +479,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1. 先看“食材（克）”和“步骤（前 400 字）”，再看“导入值”。不要只凭菜名判断。</t>
+          <t>1. 先看“食材（克）”和“步骤（前 400 字）”，再看“本批的值”。不要只凭菜名判断。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2. 在“你看完后的值”里填你认为正确的值（同意导入值也照抄一遍，不能空着），用代码：</t>
+          <t>2. 在“你看完后的值”里填你认为正确的值（同意也照抄一遍，不能空着），用代码：</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   餐型角色：protein_main / vegetable / soup / staple / one_bowl / breakfast / salad / snack / dessert / sauce / drink，并且必须在“可选角色”里；</t>
+          <t xml:space="preserve">   餐型角色：protein_main / vegetable / soup / staple / one_bowl / breakfast / salad / snack / dessert / sauce / drink；“可选角色”有内容时必须在里面，空着时任填一个；</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   是否自带主食：true 或 false（one_bowl 和 staple 是 true，其他角色是 false）；</t>
+          <t xml:space="preserve">   是否自带主食：true 或 false（one_bowl 和 staple 是 true，其他角色是 false），不要填“是/否”；</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   主要蛋白来源：用英文逗号分隔 chicken, duck, pork, beef, lamb, fish, shellfish, soy, egg, legume；没有主要蛋白填 []；</t>
+          <t xml:space="preserve">   主要蛋白来源：用逗号分隔 chicken, duck, pork, beef, lamb, fish, shellfish, soy, egg, legume；没有主要蛋白填 []；</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   看不出来、或正确的值不在可选范围里：填 null。</t>
+          <t xml:space="preserve">   看不出来、或正确的值不在可选范围里：填 null。认不出的写法会被标为“无法识别，请重填”。</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>准确率由 data-engineering/scripts/review_table_accuracy.py 计算并公开。组长看过准确率后，</t>
+          <t>准确率由 data-engineering/scripts/review_table_accuracy.py 分层计算并公开。组长看过准确率后，</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -622,7 +622,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>导入值</t>
+          <t>本批的值</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -3358,6 +3358,1239 @@
       <c r="K60" s="3" t="n"/>
       <c r="L60" s="3" t="n"/>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_441BD2095B93</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Vietnamese Pâté Chaud</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>snack_appetizer</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>pork 300.0 g（300 grams ground pork）; pate 75.0 g（75 grams pate）; onion 110.0 g（1 yellow onion, finely diced）; salt 3.0 g（1/2 teaspoon salt (or more to taste)）; black_pepper 1.1 g（1/2 teaspoon ground black pepper）; sugar 1.0 g（1/4 teaspoon sugar）; potato_starch 8.0 g（2 teaspoons potato starch）; puff_pastry 490.0 g（2 sheets of puff pastry）; egg 50.0 g（1 egg beaten）</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Filling: Combine the pork, pate, onion, potato starch and season with salt, sugar and pepper. Mix thoroughly until all of the ingredients are uniformly amalgamated. To ensure that the mixture is properly seasoned, add the salt gradually and taste after each addition by cooking a spoonful in the microwave (but without the spoon). / Preheat oven to 175°C.
+Work with one pastry sheet at time, leaving</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>protein_sources</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>pork</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="3" t="n"/>
+      <c r="K61" s="3" t="n"/>
+      <c r="L61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_03DEE14CDC60</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Hush Puppies</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>cornmeal 157.0 g（1 c. cornmeal）; flour 125.0 g（1 c. flour）; baking_powder 9.2 g（2 tsp. baking powder）; salt 6.1 g（1 tsp. salt）; garlic_salt 3.0 g（1/2 tsp. garlic salt）; onion 20.0 g（2 Tbsp. diced onion）; egg 50.0 g（1 egg）; milk 183.0 g（3/4 c. milk）</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Add and blend all ingredients. / Drop by teaspoonfuls into hot oil and fry to a golden brown. / Drain on paper towels and serve hot. / Serves 4 to 6.</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>meal_role</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>staple</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="3" t="n"/>
+      <c r="K62" s="3" t="n"/>
+      <c r="L62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_03DEE14CDC60</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Hush Puppies</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>cornmeal 157.0 g（1 c. cornmeal）; flour 125.0 g（1 c. flour）; baking_powder 9.2 g（2 tsp. baking powder）; salt 6.1 g（1 tsp. salt）; garlic_salt 3.0 g（1/2 tsp. garlic salt）; onion 20.0 g（2 Tbsp. diced onion）; egg 50.0 g（1 egg）; milk 183.0 g（3/4 c. milk）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Add and blend all ingredients. / Drop by teaspoonfuls into hot oil and fry to a golden brown. / Drain on paper towels and serve hot. / Serves 4 to 6.</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>contains_staple</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="3" t="n"/>
+      <c r="K63" s="3" t="n"/>
+      <c r="L63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_1729D7258E04</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Egg Filling For Sushi</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>egg 100.0 g（2 eggs）; flour 15.6 g（2 tablespoons flour）; sugar 25.0 g（2 tablespoons sugar）; salt 6.1 g（1 teaspoon salt）</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>In a bowl beat all ingredients together. / Heat a non stick or lightly oiled pan on a medium heat. I normally use a small frying pan to give me a 1/4 inch thick omelette. / Cook until golden on both sides. / Allow to cool and slice into 1/2 inch thick slices.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>meal_role</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>sauce</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="3" t="n"/>
+      <c r="K64" s="3" t="n"/>
+      <c r="L64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_1729D7258E04</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Egg Filling For Sushi</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>egg 100.0 g（2 eggs）; flour 15.6 g（2 tablespoons flour）; sugar 25.0 g（2 tablespoons sugar）; salt 6.1 g（1 teaspoon salt）</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>In a bowl beat all ingredients together. / Heat a non stick or lightly oiled pan on a medium heat. I normally use a small frying pan to give me a 1/4 inch thick omelette. / Cook until golden on both sides. / Allow to cool and slice into 1/2 inch thick slices.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>contains_staple</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="3" t="n"/>
+      <c r="K65" s="3" t="n"/>
+      <c r="L65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_1EF61A58359F</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Apple Casserole</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>apple 880.0 g（8 c. sliced tart apples）; cranberry 200.0 g（2 c. raw cranberries, washed）; sugar 150.0 g（3/4 c. sugar）; margarine 113.5 g（1 stick margarine）; oats 81.0 g（1 c. uncooked oatmeal）; flour 41.7 g（1/3 c. flour）; brown_sugar 110.0 g（1/2 c. brown sugar）; mixed_nuts 60.0 g（1/2 c. chopped nuts）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Into greased casserole (I use margarine for greasing), add apples and cranberries. / Sprinkle with 3/4 cup sugar (this can be done the day before and refrigerated). / Mix melted margarine, oatmeal, flour, brown sugar and nuts. / Sprinkle over apples and cranberries. / Bake approximately 1 hour in 350° oven. / Serves 12 plus. / May be used as side dish or dessert.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>protein_sources</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="3" t="n"/>
+      <c r="K66" s="3" t="n"/>
+      <c r="L66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_23DCDA368745</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Homemade Nama (Fresh) Udon Noodles</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>bread_flour 190.5 g（1 1/2 cups bread flour）; flour 187.5 g（1 1/2 cups all-purpose flour）; salt 6.1 g（1 teaspoon salt）; water 237.0 g（1 cup water）</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Combine bread flour, all-purpose flour, and salt together in a large bowl. Mix in water slowly until dough comes together into a rough ball. / Turn dough out onto a work surface and knead until smooth and elastic, about 15 minutes. Wrap dough in plastic wrap and refrigerate, at least 3 hours or overnight. / Remove dough from the refrigerator and cut in half. Dust the dough, rolling pin, and your w</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>meal_role</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>staple</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="3" t="n"/>
+      <c r="K67" s="3" t="n"/>
+      <c r="L67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_23DCDA368745</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Homemade Nama (Fresh) Udon Noodles</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>bread_flour 190.5 g（1 1/2 cups bread flour）; flour 187.5 g（1 1/2 cups all-purpose flour）; salt 6.1 g（1 teaspoon salt）; water 237.0 g（1 cup water）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Combine bread flour, all-purpose flour, and salt together in a large bowl. Mix in water slowly until dough comes together into a rough ball. / Turn dough out onto a work surface and knead until smooth and elastic, about 15 minutes. Wrap dough in plastic wrap and refrigerate, at least 3 hours or overnight. / Remove dough from the refrigerator and cut in half. Dust the dough, rolling pin, and your w</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>contains_staple</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="3" t="n"/>
+      <c r="K68" s="3" t="n"/>
+      <c r="L68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_35DC1259F6B0</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Soft Shell Tacos</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>baked_good</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>flour 125.0 g（1 c. flour）; cornmeal 78.5 g（1/2 c. cornmeal）; salt 1.5 g（1/4 tsp. salt）; egg 50.0 g（1 egg）; water 474.0 g（2 c. water）</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Mix and drop on hot griddle. / Spread thin and cook until dry on top.</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>meal_role</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>sauce</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="3" t="n"/>
+      <c r="K69" s="3" t="n"/>
+      <c r="L69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_35DC1259F6B0</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Soft Shell Tacos</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>baked_good</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>flour 125.0 g（1 c. flour）; cornmeal 78.5 g（1/2 c. cornmeal）; salt 1.5 g（1/4 tsp. salt）; egg 50.0 g（1 egg）; water 474.0 g（2 c. water）</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Mix and drop on hot griddle. / Spread thin and cook until dry on top.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>contains_staple</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="3" t="n"/>
+      <c r="K70" s="3" t="n"/>
+      <c r="L70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_4A7CC5A410F0</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Plantains In Coconut Milk</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>plantain 945.0 g（3 -4 plantains, sliced in rounds）; salt 1.5 g（1/4 teaspoon salt）; curry_powder 2.0 g（1 teaspoon curry powder）; cinnamon 1.3 g（1/2 teaspoon cinnamon）; cloves_spice 0.3 g（1/8 teaspoon clove）; coconut_milk 339.0 g（1 -2 cup coconut milk）</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Combine all ingredients except coconut milk in a heavy saucepan. / Pour in 1 cup of coconut milk and simmer over low heat until plantain is very tender and milk is absorbed. / Add more coconut milk if necessary. Serve hot.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>meal_role</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>staple</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="3" t="n"/>
+      <c r="K71" s="3" t="n"/>
+      <c r="L71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_4A7CC5A410F0</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Plantains In Coconut Milk</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>plantain 945.0 g（3 -4 plantains, sliced in rounds）; salt 1.5 g（1/4 teaspoon salt）; curry_powder 2.0 g（1 teaspoon curry powder）; cinnamon 1.3 g（1/2 teaspoon cinnamon）; cloves_spice 0.3 g（1/8 teaspoon clove）; coconut_milk 339.0 g（1 -2 cup coconut milk）</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Combine all ingredients except coconut milk in a heavy saucepan. / Pour in 1 cup of coconut milk and simmer over low heat until plantain is very tender and milk is absorbed. / Add more coconut milk if necessary. Serve hot.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>contains_staple</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="3" t="n"/>
+      <c r="K72" s="3" t="n"/>
+      <c r="L72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_561E7EDAC82C</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Cuban Black Beans</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>garlic 4.2 g（1 1/2 teaspoons chopped garlic）; olive_oil 9.0 g（2 teaspoons olive oil）; red_onion 40.0 g（1/4 cup chopped red onion）; bell_pepper 37.2 g（1/4 cup chopped red bell pepper）; carrot 32.0 g（1/4 cup chopped carrot）; jalapeno 28.0 g（2 jalapenos, seeded and chopped）; black_beans 344.0 g（2 cups cooked black beans (drained and rinsed if canned)）; coriander 1.4 g（1 1/2 teaspoons chopped fresh coriander）; lime_juice 30.2 g（2 tablespoons fresh lime juice）</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>In a skillet, heat garlic and oil over moderate heat until garlic is fragrant. / Stir in onion, bell pepper, carrot and jalapeno. / Cook mixture, stirring occasionally, until vegetables are softened. / Stir in beans, coriander, lime juice, and salt and pepper to taste and cook, stirring till heated through. / Keep warm till serving time.</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>protein_sources</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>legume</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="3" t="n"/>
+      <c r="K73" s="3" t="n"/>
+      <c r="L73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_A31F833871D7</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Bread Dumplings</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>bread 87.0 g（3 slices white bread）; butter 28.4 g（2 Tbsp. butter）; flour 187.5 g（1 1/2 c. sifted flour）; salt 18.2 g（1 Tbsp. salt）; egg 50.0 g（1 beaten egg）; milk 183.0 g（3/4 c. milk）</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Dice and fry bread in butter until crisp. / Remove and place on paper towel. / In large bowl, mix flour and salt. / Mix egg and milk and stir into flour mixture. / Form into dumplings around bread cubes, using 3 to 4 cubes per dumpling. / Drop into boiling water, taking care that dumplings do not stick. / Cover and boil gently 15 to 20 minutes or until done. / Makes 4 servings.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>meal_role</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>staple</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="3" t="n"/>
+      <c r="K74" s="3" t="n"/>
+      <c r="L74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_A31F833871D7</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Bread Dumplings</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>bread 87.0 g（3 slices white bread）; butter 28.4 g（2 Tbsp. butter）; flour 187.5 g（1 1/2 c. sifted flour）; salt 18.2 g（1 Tbsp. salt）; egg 50.0 g（1 beaten egg）; milk 183.0 g（3/4 c. milk）</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Dice and fry bread in butter until crisp. / Remove and place on paper towel. / In large bowl, mix flour and salt. / Mix egg and milk and stir into flour mixture. / Form into dumplings around bread cubes, using 3 to 4 cubes per dumpling. / Drop into boiling water, taking care that dumplings do not stick. / Cover and boil gently 15 to 20 minutes or until done. / Makes 4 servings.</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>contains_staple</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="3" t="n"/>
+      <c r="K75" s="3" t="n"/>
+      <c r="L75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_A660E279682A</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Easy Potato Dumplings</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>instant_mashed_potato 60.0 g（1 cup instant instant potato flakes）; water 237.0 g（1 cup hot water）; salt 3.0 g（1/2 teaspoon salt）; egg 50.0 g（1 egg）; flour 125.0 g（1 cup all-purpose flour）; butter 56.8 g（1/4 cup melted butter）; breadcrumbs 27.0 g（1/4 cup breadcrumbs）</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Combine Potato Buds &amp; hot water. / Add remaining ingredients in given order, mix well. / Form into 2-inch balls with hands, flour hands occasionally so dough doesn't stick. / Cook in boiling salted water until they rise to the top. / Remove dumplings from water with a slotted spoon &amp; place in butter casserole dish. / Sprinkle with bread crumbs &amp; keep layering melted butter, dumplings &amp; crumbs. / C</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>meal_role</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>staple</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="3" t="n"/>
+      <c r="K76" s="3" t="n"/>
+      <c r="L76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_A660E279682A</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Easy Potato Dumplings</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>instant_mashed_potato 60.0 g（1 cup instant instant potato flakes）; water 237.0 g（1 cup hot water）; salt 3.0 g（1/2 teaspoon salt）; egg 50.0 g（1 egg）; flour 125.0 g（1 cup all-purpose flour）; butter 56.8 g（1/4 cup melted butter）; breadcrumbs 27.0 g（1/4 cup breadcrumbs）</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Combine Potato Buds &amp; hot water. / Add remaining ingredients in given order, mix well. / Form into 2-inch balls with hands, flour hands occasionally so dough doesn't stick. / Cook in boiling salted water until they rise to the top. / Remove dumplings from water with a slotted spoon &amp; place in butter casserole dish. / Sprinkle with bread crumbs &amp; keep layering melted butter, dumplings &amp; crumbs. / C</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>contains_staple</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="3" t="n"/>
+      <c r="K77" s="3" t="n"/>
+      <c r="L77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_B8E67A023CFD</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Chtitha Batata (Algerian Potato Stew)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>garlic 12.0 g（4 cloves Garlic）; chili_pepper 45.0 g（1 small Red Chilli）; cumin 2.2 g（1 tsp Ground Cumin）; paprika 2.3 g（1 teaspoon Paprika）; black_pepper 1.1 g（1/2 teaspoon Black Pepper）; cayenne 0.9 g（1/2 teaspoon Cayenne Pepper）; salt 3.0 g（1/2 teaspoon Salt）; olive_oil 27.0 g（2 tablespoons Olive Oil）; potato 907.2 g（2 Lbs New Potatoes）; tomato_puree 15.6 g（1 tablespoon Tomato Puree）; water 500.9 g（Boiled Water）; salt 1.5 g（To taste Salt）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Combine garlic, chile pepper, cumin, paprika, black pepper, cayenne, and salt in a mortar; grind with a pestle until it forms a paste. Add olive oil and mix dersa well. / Heat a large saucepan over medium heat and stir-fry dersa until fragrant, 2 to 4 minutes. Add potato halves and stir to combine with the dersa. Stir in tomato paste. Pour in enough water to just cover the potatoes and bring to a </t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>meal_role</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>staple</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="3" t="n"/>
+      <c r="K78" s="3" t="n"/>
+      <c r="L78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_B8E67A023CFD</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Chtitha Batata (Algerian Potato Stew)</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>garlic 12.0 g（4 cloves Garlic）; chili_pepper 45.0 g（1 small Red Chilli）; cumin 2.2 g（1 tsp Ground Cumin）; paprika 2.3 g（1 teaspoon Paprika）; black_pepper 1.1 g（1/2 teaspoon Black Pepper）; cayenne 0.9 g（1/2 teaspoon Cayenne Pepper）; salt 3.0 g（1/2 teaspoon Salt）; olive_oil 27.0 g（2 tablespoons Olive Oil）; potato 907.2 g（2 Lbs New Potatoes）; tomato_puree 15.6 g（1 tablespoon Tomato Puree）; water 500.9 g（Boiled Water）; salt 1.5 g（To taste Salt）</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Combine garlic, chile pepper, cumin, paprika, black pepper, cayenne, and salt in a mortar; grind with a pestle until it forms a paste. Add olive oil and mix dersa well. / Heat a large saucepan over medium heat and stir-fry dersa until fragrant, 2 to 4 minutes. Add potato halves and stir to combine with the dersa. Stir in tomato paste. Pour in enough water to just cover the potatoes and bring to a </t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>contains_staple</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="3" t="n"/>
+      <c r="K79" s="3" t="n"/>
+      <c r="L79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_C25D9C4D878B</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Yorkshire Pudding</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>egg 100.0 g（2 eggs）; milk 488.0 g（2 c. milk）; flour 125.0 g（1 c. all purpose flour）</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Preheat oven to 350°. Combine eggs and milk in bowl. Stir in flour; mix well. Pour into greased 8 inch square pan. Bake for 30 minutes. Yield: 4 to 6 serving.</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>meal_role</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>staple</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="3" t="n"/>
+      <c r="K80" s="3" t="n"/>
+      <c r="L80" s="3" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_C25D9C4D878B</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Yorkshire Pudding</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>egg 100.0 g（2 eggs）; milk 488.0 g（2 c. milk）; flour 125.0 g（1 c. all purpose flour）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Preheat oven to 350°. Combine eggs and milk in bowl. Stir in flour; mix well. Pour into greased 8 inch square pan. Bake for 30 minutes. Yield: 4 to 6 serving.</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>contains_staple</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="3" t="n"/>
+      <c r="K81" s="3" t="n"/>
+      <c r="L81" s="3" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_C8B759477F8B</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Gözleme (Turkish Flatbread)</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>flour 656.2 g（5¼ cups (600 grams) all-purpose flour）; salt 15.2 g（2½ teaspoons (15 grams) salt）; yeast 6.3 g（2 teaspoons (7 grams) dry yeast）; sugar 4.2 g（1 teaspoon (4 grams) white granulated sugar）; water 296.2 g（1¼ cups (300 grams) water）; vegetable_oil 109.0 g（½ cup (100 grams) oil）; butter 75.7 g（⅓ cup (65 grams) butter）</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Sift flour in a large bowl, reserving 1 cup of flour. / Sprinkle with salt and mix. Make a well in the centre. / Combine yeast and sugar in a small bowl. Stir in ¼ cup warm water. / Pour the liquid into the well in the centre of the flour. / Cover yeast with some flour. Let stand for 10 minutes to rise. / Stir in remaining liquid, blending thoroughly. Knead for 5 minutes to form a medium-soft doug</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>meal_role</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>staple</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="3" t="n"/>
+      <c r="K82" s="3" t="n"/>
+      <c r="L82" s="3" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_C8B759477F8B</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Gözleme (Turkish Flatbread)</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>flour 656.2 g（5¼ cups (600 grams) all-purpose flour）; salt 15.2 g（2½ teaspoons (15 grams) salt）; yeast 6.3 g（2 teaspoons (7 grams) dry yeast）; sugar 4.2 g（1 teaspoon (4 grams) white granulated sugar）; water 296.2 g（1¼ cups (300 grams) water）; vegetable_oil 109.0 g（½ cup (100 grams) oil）; butter 75.7 g（⅓ cup (65 grams) butter）</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Sift flour in a large bowl, reserving 1 cup of flour. / Sprinkle with salt and mix. Make a well in the centre. / Combine yeast and sugar in a small bowl. Stir in ¼ cup warm water. / Pour the liquid into the well in the centre of the flour. / Cover yeast with some flour. Let stand for 10 minutes to rise. / Stir in remaining liquid, blending thoroughly. Knead for 5 minutes to form a medium-soft doug</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>contains_staple</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="3" t="n"/>
+      <c r="K83" s="3" t="n"/>
+      <c r="L83" s="3" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_D1A78AFA0C85</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Teenage Sloppy Joes</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>beef 907.2 g（2 lb. ground beef）; bell_pepper 149.0 g（1 c. green peppers）; onion 160.0 g（1 c. chopped onion）; bbq_sauce 520.0 g（2 c. barbecue sauce）; water 474.0 g（2 c. water）; oats 81.0 g（1 c. oats）; flour 15.6 g（2 Tbsp. flour）; salt 6.1 g（1 tsp. salt）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Combine beef, green peppers and onion in skillet until brown. Add mixed oats, flour, salt and water with barbecue sauce and cook until done. / This recipe will serve 6 people.</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>meal_role</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>protein_main</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="3" t="n"/>
+      <c r="K84" s="3" t="n"/>
+      <c r="L84" s="3" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_D1A78AFA0C85</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Teenage Sloppy Joes</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>beef 907.2 g（2 lb. ground beef）; bell_pepper 149.0 g（1 c. green peppers）; onion 160.0 g（1 c. chopped onion）; bbq_sauce 520.0 g（2 c. barbecue sauce）; water 474.0 g（2 c. water）; oats 81.0 g（1 c. oats）; flour 15.6 g（2 Tbsp. flour）; salt 6.1 g（1 tsp. salt）</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Combine beef, green peppers and onion in skillet until brown. Add mixed oats, flour, salt and water with barbecue sauce and cook until done. / This recipe will serve 6 people.</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>contains_staple</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="3" t="n"/>
+      <c r="K85" s="3" t="n"/>
+      <c r="L85" s="3" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_F9AC64939A2C</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Welsh Rarebit</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>butter 21.3 g（1 1/2 Tbsp. butter）; flour 11.7 g（1 1/2 Tbsp. flour）; milk 366.0 g（1 1/2 c. milk）; cheddar 113.0 g（1 c. grated Cheddar cheese）; salt 3.0 g（1/2 tsp. salt）; mustard 2.6 g（1/2 tsp. mustard）; paprika 0.3 g（1/8 tsp. paprika）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Make white sauce of butter, flour and milk. / Add cheese and stir over low heat until cheese is melted. / Add seasonings. / Serve hot over buttered toast or crackers.</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>protein_sources</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="3" t="n"/>
+      <c r="K86" s="3" t="n"/>
+      <c r="L86" s="3" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_FB5F31874C8A</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Fresh Ramen Egg Noodles From Scratch</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>flour 62.5 g（1/2 cup unbleached all-purpose flour）; semolina_flour 83.5 g（1/2 cup semolina flour）; salt 1.5 g（1/4 teaspoon fine sea salt）; garlic_powder 0.7 g（1/4 teaspoon garlic powder）; egg 50.0 g（1 egg, beaten）; sesame_oil 13.6 g（1 tablespoon sesame oil）; water 118.5 g（1/2 cup water, or as needed）</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Place all-purpose flour, semolina flour, sea salt, and garlic powder in a food processor. Pulse to blend well. Reduce speed to low. Add egg and sesame oil through the feeder. / Increase speed to high. Add 1 tablespoon water, reduce speed to low, and blend. Set speed back to high; continue adding water 1 tablespoon at a time and blending on low until dough forms into a ball. Stop adding water immed</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>meal_role</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>staple</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="3" t="n"/>
+      <c r="K87" s="3" t="n"/>
+      <c r="L87" s="3" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_FB5F31874C8A</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Fresh Ramen Egg Noodles From Scratch</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>flour 62.5 g（1/2 cup unbleached all-purpose flour）; semolina_flour 83.5 g（1/2 cup semolina flour）; salt 1.5 g（1/4 teaspoon fine sea salt）; garlic_powder 0.7 g（1/4 teaspoon garlic powder）; egg 50.0 g（1 egg, beaten）; sesame_oil 13.6 g（1 tablespoon sesame oil）; water 118.5 g（1/2 cup water, or as needed）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Place all-purpose flour, semolina flour, sea salt, and garlic powder in a food processor. Pulse to blend well. Reduce speed to low. Add egg and sesame oil through the feeder. / Increase speed to high. Add 1 tablespoon water, reduce speed to low, and blend. Set speed back to high; continue adding water 1 tablespoon at a time and blending on low until dough forms into a ball. Stop adding water immed</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>contains_staple</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="3" t="n"/>
+      <c r="K88" s="3" t="n"/>
+      <c r="L88" s="3" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data-engineering/docs/review-table-20261024/sample.xlsx
+++ b/data-engineering/docs/review-table-20261024/sample.xlsx
@@ -493,7 +493,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   餐型角色：protein_main / vegetable / soup / staple / one_bowl / breakfast / salad / snack / dessert / sauce / drink；“可选角色”有内容时必须在里面，空着时任填一个；</t>
+          <t xml:space="preserve">   餐型角色：protein_main / vegetable / soup / staple / one_bowl / breakfast / salad / snack / dessert / sauce / drink 之一；</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   看不出来、或正确的值不在可选范围里：填 null。认不出的写法会被标为“无法识别，请重填”。</t>
+          <t xml:space="preserve">   看不出来：填 null。认不出的写法会被标为“无法识别，请重填”。</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -578,10 +578,9 @@
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -627,20 +626,15 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>可选角色</t>
+          <t>你看完后的值</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>你看完后的值</t>
+          <t>已亲自核对（填 是）</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>已亲自核对（填 是）</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -652,12 +646,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>RCP2_5D84F859E558</t>
+          <t>RCP2_00100560483E</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>English Popovers</t>
+          <t>Swedish Crescents</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -667,12 +661,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>egg 100.0 g（2 eggs）; milk 244.0 g（1 c. milk）; flour 125.0 g（1 c. flour, sifted）</t>
+          <t>butter 227.0 g（1 c. butter）; powdered_sugar 60.0 g（1/2 c. confectioners sugar）; vanilla 4.3 g（1 tsp. vanilla）; flour 218.8 g（1 3/4 c. sifted plain flour）; pecan 119.0 g（1 c. finely chopped pecans）; salt 1.5 g（1/4 tsp. salt）</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Put all ingredients in a blender. / Blend until smooth. / Fill 8 well-greased muffin tins or custard cups. / Bake at 400° for 10 minutes, then lower oven temperature to 350° for 20 minutes longer. / Serve warm with butter and jam.</t>
+          <t>Cream butter and confectioners sugar. / Add vanilla, flour, nuts and salt; mix. / Chill well. / Shape dough into crescents, using 1/2 teaspoon dough. / Put on cookie sheet. / Bake at 300° for 18 to 20 minutes. / Check to be sure they do not brown. / When done, roll in 1 cup confectioners sugar to which 1 teaspoon of vanilla has been added. / Makes between 6 and 7 dozen.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -682,17 +676,12 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>breakfast</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>protein_main / staple / one_bowl / breakfast / snack / dessert</t>
-        </is>
-      </c>
+          <t>dessert</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="n"/>
       <c r="J2" s="3" t="n"/>
       <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -700,12 +689,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>RCP2_5D84F859E558</t>
+          <t>RCP2_00100560483E</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>English Popovers</t>
+          <t>Swedish Crescents</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -715,12 +704,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>egg 100.0 g（2 eggs）; milk 244.0 g（1 c. milk）; flour 125.0 g（1 c. flour, sifted）</t>
+          <t>butter 227.0 g（1 c. butter）; powdered_sugar 60.0 g（1/2 c. confectioners sugar）; vanilla 4.3 g（1 tsp. vanilla）; flour 218.8 g（1 3/4 c. sifted plain flour）; pecan 119.0 g（1 c. finely chopped pecans）; salt 1.5 g（1/4 tsp. salt）</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Put all ingredients in a blender. / Blend until smooth. / Fill 8 well-greased muffin tins or custard cups. / Bake at 400° for 10 minutes, then lower oven temperature to 350° for 20 minutes longer. / Serve warm with butter and jam.</t>
+          <t>Cream butter and confectioners sugar. / Add vanilla, flour, nuts and salt; mix. / Chill well. / Shape dough into crescents, using 1/2 teaspoon dough. / Put on cookie sheet. / Bake at 300° for 18 to 20 minutes. / Check to be sure they do not brown. / When done, roll in 1 cup confectioners sugar to which 1 teaspoon of vanilla has been added. / Makes between 6 and 7 dozen.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -733,10 +722,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -744,12 +732,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>RCP2_00100560483E</t>
+          <t>RCP2_02ED221BB8C3</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Swedish Crescents</t>
+          <t>Snowballs(Swedish)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -759,12 +747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>butter 227.0 g（1 c. butter）; powdered_sugar 60.0 g（1/2 c. confectioners sugar）; vanilla 4.3 g（1 tsp. vanilla）; flour 218.8 g（1 3/4 c. sifted plain flour）; pecan 119.0 g（1 c. finely chopped pecans）; salt 1.5 g（1/4 tsp. salt）</t>
+          <t>butter 227.0 g（1 c. butter）; sugar 50.0 g（4 Tbsp. sugar）; flour 250.0 g（2 c. flour）; vanilla 4.3 g（1 tsp. vanilla）; walnut 117.0 g（1 c. walnuts）; pecan 119.0 g（1 c. pecans）</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Cream butter and confectioners sugar. / Add vanilla, flour, nuts and salt; mix. / Chill well. / Shape dough into crescents, using 1/2 teaspoon dough. / Put on cookie sheet. / Bake at 300° for 18 to 20 minutes. / Check to be sure they do not brown. / When done, roll in 1 cup confectioners sugar to which 1 teaspoon of vanilla has been added. / Makes between 6 and 7 dozen.</t>
+          <t>Mix all ingredients. / Place in balls on lightly greased cookie sheet. / Bake at 250° for 1 hour. / (Roll in hand. / If crumbles, it is not done. / Pick up and test.) / Once done, roll in powdered sugar twice, once when hot, once when cool.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -777,14 +765,9 @@
           <t>dessert</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>one_bowl / breakfast / snack / dessert</t>
-        </is>
-      </c>
+      <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -792,12 +775,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>RCP2_00100560483E</t>
+          <t>RCP2_02ED221BB8C3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Swedish Crescents</t>
+          <t>Snowballs(Swedish)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -807,12 +790,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>butter 227.0 g（1 c. butter）; powdered_sugar 60.0 g（1/2 c. confectioners sugar）; vanilla 4.3 g（1 tsp. vanilla）; flour 218.8 g（1 3/4 c. sifted plain flour）; pecan 119.0 g（1 c. finely chopped pecans）; salt 1.5 g（1/4 tsp. salt）</t>
+          <t>butter 227.0 g（1 c. butter）; sugar 50.0 g（4 Tbsp. sugar）; flour 250.0 g（2 c. flour）; vanilla 4.3 g（1 tsp. vanilla）; walnut 117.0 g（1 c. walnuts）; pecan 119.0 g（1 c. pecans）</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Cream butter and confectioners sugar. / Add vanilla, flour, nuts and salt; mix. / Chill well. / Shape dough into crescents, using 1/2 teaspoon dough. / Put on cookie sheet. / Bake at 300° for 18 to 20 minutes. / Check to be sure they do not brown. / When done, roll in 1 cup confectioners sugar to which 1 teaspoon of vanilla has been added. / Makes between 6 and 7 dozen.</t>
+          <t>Mix all ingredients. / Place in balls on lightly greased cookie sheet. / Bake at 250° for 1 hour. / (Roll in hand. / If crumbles, it is not done. / Pick up and test.) / Once done, roll in powdered sugar twice, once when hot, once when cool.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -825,10 +808,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -836,12 +818,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>RCP2_02ED221BB8C3</t>
+          <t>RCP2_0CFF755F4ED0</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Snowballs(Swedish)</t>
+          <t>Mexican Wedding Cakes</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -851,12 +833,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>butter 227.0 g（1 c. butter）; sugar 50.0 g（4 Tbsp. sugar）; flour 250.0 g（2 c. flour）; vanilla 4.3 g（1 tsp. vanilla）; walnut 117.0 g（1 c. walnuts）; pecan 119.0 g（1 c. pecans）</t>
+          <t>butter 227.0 g（1 c. butter）; powdered_sugar 60.0 g（1/2 c. powdered sugar）; flour 218.8 g（1 3/4 c. flour）; pecan 59.5 g（1/2 c. chopped pecans）; vanilla 2.2 g（1/2 tsp. vanilla）</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Mix all ingredients. / Place in balls on lightly greased cookie sheet. / Bake at 250° for 1 hour. / (Roll in hand. / If crumbles, it is not done. / Pick up and test.) / Once done, roll in powdered sugar twice, once when hot, once when cool.</t>
+          <t>Mix butter and powdered sugar. / Add other ingredients and mix thoroughly. / Chill dough. / Roll into small balls and bake until done, about 8 to 10 minutes, at 375°. / When done, roll in powdered sugar.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -869,14 +851,9 @@
           <t>dessert</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>one_bowl / breakfast / snack / dessert</t>
-        </is>
-      </c>
+      <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -884,12 +861,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>RCP2_02ED221BB8C3</t>
+          <t>RCP2_0CFF755F4ED0</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Snowballs(Swedish)</t>
+          <t>Mexican Wedding Cakes</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -899,12 +876,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>butter 227.0 g（1 c. butter）; sugar 50.0 g（4 Tbsp. sugar）; flour 250.0 g（2 c. flour）; vanilla 4.3 g（1 tsp. vanilla）; walnut 117.0 g（1 c. walnuts）; pecan 119.0 g（1 c. pecans）</t>
+          <t>butter 227.0 g（1 c. butter）; powdered_sugar 60.0 g（1/2 c. powdered sugar）; flour 218.8 g（1 3/4 c. flour）; pecan 59.5 g（1/2 c. chopped pecans）; vanilla 2.2 g（1/2 tsp. vanilla）</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Mix all ingredients. / Place in balls on lightly greased cookie sheet. / Bake at 250° for 1 hour. / (Roll in hand. / If crumbles, it is not done. / Pick up and test.) / Once done, roll in powdered sugar twice, once when hot, once when cool.</t>
+          <t>Mix butter and powdered sugar. / Add other ingredients and mix thoroughly. / Chill dough. / Roll into small balls and bake until done, about 8 to 10 minutes, at 375°. / When done, roll in powdered sugar.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -917,10 +894,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -928,27 +904,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>RCP2_0CFF755F4ED0</t>
+          <t>RCP2_0DE59ED69BBF</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Mexican Wedding Cakes</t>
+          <t>Stuffed Bell Peppers</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>baked_good</t>
+          <t>main</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>butter 227.0 g（1 c. butter）; powdered_sugar 60.0 g（1/2 c. powdered sugar）; flour 218.8 g（1 3/4 c. flour）; pecan 59.5 g（1/2 c. chopped pecans）; vanilla 2.2 g（1/2 tsp. vanilla）</t>
+          <t>bell_pepper 2160.0 g（18 small bell peppers）; rice 118.5 g（3/4 c. cooked rice）; beef 680.4 g（1 1/2 lb. ground beef）; bell_pepper 74.5 g（1/2 c. chopped bell peppers）; onion 53.3 g（1/3 c. chopped onion）; cayenne 0.4 g（1/4 tsp. ground red peppers）; black_pepper 0.6 g（1/4 tsp. black pepper）; salt 6.1 g（1 tsp. salt）</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Mix butter and powdered sugar. / Add other ingredients and mix thoroughly. / Chill dough. / Roll into small balls and bake until done, about 8 to 10 minutes, at 375°. / When done, roll in powdered sugar.</t>
+          <t>Cut thin slice from top of each green pepper; remove stems and seeds. / In saucepan over medium heat, in 1-inch boiling water, heat peppers to boiling. / Reduce heat to low. / Cover; simmer 5 minutes or until peppers are tender to crisp. / Drain. / In shallow baking dish, arrange peppers. / Meanwhile, in a skillet, brown meat and cook with chopped peppers and onions until tender. / Add remaining i</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -958,17 +934,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>dessert</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>one_bowl / breakfast / snack / dessert</t>
-        </is>
-      </c>
+          <t>protein_main</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -976,27 +947,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>RCP2_0CFF755F4ED0</t>
+          <t>RCP2_0DE59ED69BBF</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Mexican Wedding Cakes</t>
+          <t>Stuffed Bell Peppers</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>baked_good</t>
+          <t>main</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>butter 227.0 g（1 c. butter）; powdered_sugar 60.0 g（1/2 c. powdered sugar）; flour 218.8 g（1 3/4 c. flour）; pecan 59.5 g（1/2 c. chopped pecans）; vanilla 2.2 g（1/2 tsp. vanilla）</t>
+          <t>bell_pepper 2160.0 g（18 small bell peppers）; rice 118.5 g（3/4 c. cooked rice）; beef 680.4 g（1 1/2 lb. ground beef）; bell_pepper 74.5 g（1/2 c. chopped bell peppers）; onion 53.3 g（1/3 c. chopped onion）; cayenne 0.4 g（1/4 tsp. ground red peppers）; black_pepper 0.6 g（1/4 tsp. black pepper）; salt 6.1 g（1 tsp. salt）</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Mix butter and powdered sugar. / Add other ingredients and mix thoroughly. / Chill dough. / Roll into small balls and bake until done, about 8 to 10 minutes, at 375°. / When done, roll in powdered sugar.</t>
+          <t>Cut thin slice from top of each green pepper; remove stems and seeds. / In saucepan over medium heat, in 1-inch boiling water, heat peppers to boiling. / Reduce heat to low. / Cover; simmer 5 minutes or until peppers are tender to crisp. / Drain. / In shallow baking dish, arrange peppers. / Meanwhile, in a skillet, brown meat and cook with chopped peppers and onions until tender. / Add remaining i</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1009,10 +980,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1020,27 +990,27 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>RCP2_229B831CE6C7</t>
+          <t>RCP2_12D50BBDB52E</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Mexican Wedding Bells</t>
+          <t>Eggplant A La Parmesan</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>baked_good</t>
+          <t>main</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>butter 227.0 g（1 c. butter, softened）; powdered_sugar 15.0 g（2 Tbsp. confectioners sugar）; cake_flour 110.0 g（1 c. cake flour）; pecan 119.0 g（1 c. chopped pecans）; vanilla 4.3 g（1 tsp. vanilla）</t>
+          <t>eggplant 300.0 g（1 medium eggplant, peeled and sliced in 1/2-inch slices）; tomato 369.0 g（3 large tomatoes, peeled and sliced）; onion 110.0 g（1 large onion, sliced and separated into rings）; margarine 170.2 g（3/4 c. margarine, melted）; basil 0.2 g（1/2 tsp. basil）; garlic_salt 4.5 g（3/4 tsp. garlic salt）; mozzarella 226.8 g（1/2 lb. Mozzarella cheese, shredded）; bread 116.0 g（4 slices bread (made into crumbs)）; parmesan 31.2 g（4 to 6 Tbsp. Parmesan cheese）</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Cream together butter and sugar until light and fluffy. / Add flour, pecans and vanilla. / Roll dough into 1-inch balls. / Place on greased sheet pan and flatten slightly. / Bake at 300° for 45 minutes. / Roll in additional confectioners sugar while hot. / When cool, roll in sugar again. / Yields 25 to 30 balls.</t>
+          <t xml:space="preserve">Preheat oven to 450°. / Arrange eggplant in the bottom of a 9 x 13-inch aluminum pan or Pyrex dish. / Top with onion, then tomatoes. Drizzle 1/2 cup margarine over entire casserole. / Sprinkle with basil and garlic salt. / Cover and bake for 20 to 30 minutes. Remove from oven and top with Mozzarella cheese. / Toss crumbs with 1/4 cup melted margarine and spread over casserole. / Top with Parmesan </t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1050,17 +1020,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>dessert</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>staple / one_bowl / breakfast / snack / dessert</t>
-        </is>
-      </c>
+          <t>vegetable</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1068,27 +1033,27 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>RCP2_229B831CE6C7</t>
+          <t>RCP2_12D50BBDB52E</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Mexican Wedding Bells</t>
+          <t>Eggplant A La Parmesan</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>baked_good</t>
+          <t>main</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>butter 227.0 g（1 c. butter, softened）; powdered_sugar 15.0 g（2 Tbsp. confectioners sugar）; cake_flour 110.0 g（1 c. cake flour）; pecan 119.0 g（1 c. chopped pecans）; vanilla 4.3 g（1 tsp. vanilla）</t>
+          <t>eggplant 300.0 g（1 medium eggplant, peeled and sliced in 1/2-inch slices）; tomato 369.0 g（3 large tomatoes, peeled and sliced）; onion 110.0 g（1 large onion, sliced and separated into rings）; margarine 170.2 g（3/4 c. margarine, melted）; basil 0.2 g（1/2 tsp. basil）; garlic_salt 4.5 g（3/4 tsp. garlic salt）; mozzarella 226.8 g（1/2 lb. Mozzarella cheese, shredded）; bread 116.0 g（4 slices bread (made into crumbs)）; parmesan 31.2 g（4 to 6 Tbsp. Parmesan cheese）</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Cream together butter and sugar until light and fluffy. / Add flour, pecans and vanilla. / Roll dough into 1-inch balls. / Place on greased sheet pan and flatten slightly. / Bake at 300° for 45 minutes. / Roll in additional confectioners sugar while hot. / When cool, roll in sugar again. / Yields 25 to 30 balls.</t>
+          <t xml:space="preserve">Preheat oven to 450°. / Arrange eggplant in the bottom of a 9 x 13-inch aluminum pan or Pyrex dish. / Top with onion, then tomatoes. Drizzle 1/2 cup margarine over entire casserole. / Sprinkle with basil and garlic salt. / Cover and bake for 20 to 30 minutes. Remove from oven and top with Mozzarella cheese. / Toss crumbs with 1/4 cup melted margarine and spread over casserole. / Top with Parmesan </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1101,10 +1066,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
+      <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1112,27 +1076,27 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>RCP2_44C42897EBAD</t>
+          <t>RCP2_130F971CF821</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Peruvian Alfajores</t>
+          <t>Ukrainian Bukovinian Nachynka (Cornbread Dressing)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>baked_good</t>
+          <t>side</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>flour 250.0 g（2 cups all-purpose flour）; powdered_sugar 30.0 g（1/4 cup confectioners' sugar）; shortening 153.8 g（3/4 cup vegetable shortening, chilled）; caramel 80.0 g（1/4 cup dulce de leche）; powdered_sugar 15.0 g（Confectioners' sugar）</t>
+          <t>onion 110.0 g（1 small onion, chopped fine）; butter 42.6 g（3 tablespoons butter）; cornmeal 157.0 g（1 cup cornmeal）; salt 6.1 g（1 teaspoon salt）; sugar 4.2 g（1 teaspoon sugar）; black_pepper 1.1 g（1/2 teaspoon pepper）; cinnamon 0.7 g（1/4 teaspoon cinnamon, if desired）; milk 854.0 g（3 1/2 cups scalded milk）; cream 119.0 g（1/2 cup light cream）; egg 125.0 g（2 -3 eggs, well beaten）</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Preheat oven to 350 degrees F (175 degrees C). / Sift flour and 1/4 cup confectioners' sugar together into a bowl. Rub the shortening into the flour until completely incorporated to form a dough. Roll out on a floured surface to 1/4-inch thick, then cut into 1 to 1 1/2-inch circles with a small, round cookie cutter. Place circles onto an ungreased baking sheet, and poke each twice with a fork. / B</t>
+          <t>Cook the onion in the butter until it is tender but not brown. / Add the corn meal along with the salt, sugar, pepper, and cinnamon, and mix them to coat the cereal thoroughly with the butter. / Pour in the scalded milk gradually and stir briskly until the mixture is smooth and free of lumps. / Cook until it thickens. / Remove it from the range and blend in the cream. / Beat the eggs well and fold</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1142,17 +1106,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>dessert</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>one_bowl / breakfast / snack / dessert</t>
-        </is>
-      </c>
+          <t>staple</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1160,27 +1119,27 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>RCP2_44C42897EBAD</t>
+          <t>RCP2_130F971CF821</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Peruvian Alfajores</t>
+          <t>Ukrainian Bukovinian Nachynka (Cornbread Dressing)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>baked_good</t>
+          <t>side</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>flour 250.0 g（2 cups all-purpose flour）; powdered_sugar 30.0 g（1/4 cup confectioners' sugar）; shortening 153.8 g（3/4 cup vegetable shortening, chilled）; caramel 80.0 g（1/4 cup dulce de leche）; powdered_sugar 15.0 g（Confectioners' sugar）</t>
+          <t>onion 110.0 g（1 small onion, chopped fine）; butter 42.6 g（3 tablespoons butter）; cornmeal 157.0 g（1 cup cornmeal）; salt 6.1 g（1 teaspoon salt）; sugar 4.2 g（1 teaspoon sugar）; black_pepper 1.1 g（1/2 teaspoon pepper）; cinnamon 0.7 g（1/4 teaspoon cinnamon, if desired）; milk 854.0 g（3 1/2 cups scalded milk）; cream 119.0 g（1/2 cup light cream）; egg 125.0 g（2 -3 eggs, well beaten）</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Preheat oven to 350 degrees F (175 degrees C). / Sift flour and 1/4 cup confectioners' sugar together into a bowl. Rub the shortening into the flour until completely incorporated to form a dough. Roll out on a floured surface to 1/4-inch thick, then cut into 1 to 1 1/2-inch circles with a small, round cookie cutter. Place circles onto an ungreased baking sheet, and poke each twice with a fork. / B</t>
+          <t>Cook the onion in the butter until it is tender but not brown. / Add the corn meal along with the salt, sugar, pepper, and cinnamon, and mix them to coat the cereal thoroughly with the butter. / Pour in the scalded milk gradually and stir briskly until the mixture is smooth and free of lumps. / Cook until it thickens. / Remove it from the range and blend in the cream. / Beat the eggs well and fold</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1190,13 +1149,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n"/>
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1204,27 +1162,27 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>RCP2_A96FC949077E</t>
+          <t>RCP2_1554F9789729</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Moroccan Lentils And Couscous</t>
+          <t>Banh Mi Hotdog</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>main</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>lentil 192.0 g（1 cup lentils, uncooked）; garlic 12.0 g（4 garlic cloves, crushed）; cumin 2.2 g（1 teaspoon cumin, ground）; salt 3.0 g（1/2 teaspoon salt）; black_pepper 0.3 g（1/8 teaspoon pepper）; cinnamon 0.2 g（1/16 teaspoon ground cinnamon）; bay_leaf 0.2 g（1 bay leaf）; water 711.0 g（3 cups water）; vegetable_oil 9.1 g（2 teaspoons vegetable oil）; onion 320.0 g（2 cups onions, cut in thin slices）; couscous 86.5 g（1/2 cup couscous, uncooked）</t>
+          <t>sausage 340.0 g（4 None pork sausages）; carrot 61.0 g（1 large carrot, peeled and grated）; cilantro 8.0 g（1/2 cup chopped cilantro）; green_onion 30.0 g（2 None green onions, shredded）; lime_juice 30.2 g（2 tbsp lime juice）; fish_sauce 18.0 g（1 tbsp fish sauce）; sesame_oil 2.3 g（1/2 tsp sesame oil）; baguette 60.0 g（1 None baguette, cut into 4, split lengthwise）; sweet_chili_sauce 60.0 g（None None Sweet chili sauce, fried onions, to serve）</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Place the lentils in a medium saucepan. / Add garlic, spices, and 3 cups of water. Bring to a boil over medium heat, stirring occasionally. / Reduce heat to low, cover, and simmer 40 minutes, stirring once halfway through cooking time. / While lentils are cooking, bring 1 cup of water to a boil in a small saucepan. / Remove from heat, stir in couscous, cover, and set aside for 15 minutes. / Heat o</t>
+          <t>Heat a skillet on medium-high heat. Cook the sausages for 8-10 mins, turning, until browned and cooked through. / Toss the carrot, cilantro, onions, lime juice, fish sauce and sesame oil in a medium bowl. / Fill each baguette with the carrot mixture and a sausage. Drizzle with sweet chili sauce and sprinkle with fried onions to serve.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1237,14 +1195,9 @@
           <t>one_bowl</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>soup / staple / one_bowl / breakfast / snack / dessert / sauce / drink</t>
-        </is>
-      </c>
+      <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1252,27 +1205,27 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>RCP2_A96FC949077E</t>
+          <t>RCP2_1554F9789729</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Moroccan Lentils And Couscous</t>
+          <t>Banh Mi Hotdog</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>main</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>lentil 192.0 g（1 cup lentils, uncooked）; garlic 12.0 g（4 garlic cloves, crushed）; cumin 2.2 g（1 teaspoon cumin, ground）; salt 3.0 g（1/2 teaspoon salt）; black_pepper 0.3 g（1/8 teaspoon pepper）; cinnamon 0.2 g（1/16 teaspoon ground cinnamon）; bay_leaf 0.2 g（1 bay leaf）; water 711.0 g（3 cups water）; vegetable_oil 9.1 g（2 teaspoons vegetable oil）; onion 320.0 g（2 cups onions, cut in thin slices）; couscous 86.5 g（1/2 cup couscous, uncooked）</t>
+          <t>sausage 340.0 g（4 None pork sausages）; carrot 61.0 g（1 large carrot, peeled and grated）; cilantro 8.0 g（1/2 cup chopped cilantro）; green_onion 30.0 g（2 None green onions, shredded）; lime_juice 30.2 g（2 tbsp lime juice）; fish_sauce 18.0 g（1 tbsp fish sauce）; sesame_oil 2.3 g（1/2 tsp sesame oil）; baguette 60.0 g（1 None baguette, cut into 4, split lengthwise）; sweet_chili_sauce 60.0 g（None None Sweet chili sauce, fried onions, to serve）</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Place the lentils in a medium saucepan. / Add garlic, spices, and 3 cups of water. Bring to a boil over medium heat, stirring occasionally. / Reduce heat to low, cover, and simmer 40 minutes, stirring once halfway through cooking time. / While lentils are cooking, bring 1 cup of water to a boil in a small saucepan. / Remove from heat, stir in couscous, cover, and set aside for 15 minutes. / Heat o</t>
+          <t>Heat a skillet on medium-high heat. Cook the sausages for 8-10 mins, turning, until browned and cooked through. / Toss the carrot, cilantro, onions, lime juice, fish sauce and sesame oil in a medium bowl. / Fill each baguette with the carrot mixture and a sausage. Drizzle with sweet chili sauce and sprinkle with fried onions to serve.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1285,10 +1238,9 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
+      <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1296,91 +1248,85 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>RCP2_956FD7177508</t>
+          <t>RCP2_1722D847EECE</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Ramen Hot And Sour Soup</t>
+          <t>Southern Spoon Bread</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>soup</t>
+          <t>side</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>ramen 85.0 g（1 (3 ounce) package ramen noodles）; water 474.0 g（2 cups water）; mushroom 8.8 g（1/8 cup mushroom, thinly sliced）; rice_vinegar 16.1 g（1 tablespoon rice vinegar）; chili_sauce 0.6 g（1/8 teaspoon chili sauce）; egg 50.0 g（1 egg, beaten）; meat 17.5 g（1/8 cup meat, cooked, sliced thinly. (optional)）; green_onion 15.0 g（1 green onion, light and dark green parts, sliced thin）</t>
+          <t>milk 488.0 g（2 c. milk）; cornmeal 157.0 g（1 c. corn meal）; butter 56.8 g（4 Tbsp. butter）; egg 200.0 g（4 eggs, separated）; salt 18.2 g（1 Tbsp. salt）</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Put 2 cups of warm water in saucepan. Add Ramen Noodles and Mushrooms. Bring to boil. / Add Rice Vinegar and Chili Sauce, cook till noodles are tender, about 5-7 minutes. Turn heat down to medium. / Add the sliced meat if desired. You can use beef, pork, or uncooked small shrimp. / Very slowly drizzle in the beaten egg so that it kinda forms a solid mass on top of the soup. Once the egg is kinda s</t>
+          <t>Pour milk into top of double boiler and cook until it almost comes to a boil. / Slowly add corn meal, stirring constantly. / Cook until mixture is thick and smooth, approximately 1 minute. / Add butter and salt and cool slightly. / Beat yolks and add to corn meal mixture. / Beat egg whites until stiff and fold into corn meal. Pour into buttered casserole dish and bake in preheated 375° oven for 35</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>protein_sources</t>
+          <t>meal_role</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>egg</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
+          <t>staple</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>RCP2_75BFE1C39E34</t>
+          <t>RCP2_1722D847EECE</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Taco Casserole</t>
+          <t>Southern Spoon Bread</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>side</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>mashed_potatoes 420.0 g（2 c. instant mashed potatoes）; sour_cream 345.0 g（1 1/2 c. sour cream）; water 59.2 g（1/4 c. water）</t>
+          <t>milk 488.0 g（2 c. milk）; cornmeal 157.0 g（1 c. corn meal）; butter 56.8 g（4 Tbsp. butter）; egg 200.0 g（4 eggs, separated）; salt 18.2 g（1 Tbsp. salt）</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>For crust, mix potatoes, sour cream and water and pat into bottom of 9 x 12-inch pan. / Bake at 350° for 20 minutes or until edges start browning.</t>
+          <t>Pour milk into top of double boiler and cook until it almost comes to a boil. / Slowly add corn meal, stirring constantly. / Cook until mixture is thick and smooth, approximately 1 minute. / Add butter and salt and cool slightly. / Beat yolks and add to corn meal mixture. / Beat egg whites until stiff and fold into corn meal. Pour into buttered casserole dish and bake in preheated 375° oven for 35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>meal_role</t>
+          <t>contains_staple</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>sauce</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>soup / staple / one_bowl / breakfast / snack / dessert / sauce / drink</t>
-        </is>
-      </c>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="n"/>
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1388,163 +1334,156 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>RCP2_75BFE1C39E34</t>
+          <t>RCP2_1729D7258E04</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Taco Casserole</t>
+          <t>Egg Filling For Sushi</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>side</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>mashed_potatoes 420.0 g（2 c. instant mashed potatoes）; sour_cream 345.0 g（1 1/2 c. sour cream）; water 59.2 g（1/4 c. water）</t>
+          <t>egg 100.0 g（2 eggs）; flour 15.6 g（2 tablespoons flour）; sugar 25.0 g（2 tablespoons sugar）; salt 6.1 g（1 teaspoon salt）</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>For crust, mix potatoes, sour cream and water and pat into bottom of 9 x 12-inch pan. / Bake at 350° for 20 minutes or until edges start browning.</t>
+          <t>In a bowl beat all ingredients together. / Heat a non stick or lightly oiled pan on a medium heat. I normally use a small frying pan to give me a 1/4 inch thick omelette. / Cook until golden on both sides. / Allow to cool and slice into 1/2 inch thick slices.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>contains_staple</t>
+          <t>meal_role</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
+          <t>sauce</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="n"/>
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>RCP2_8F83C05E5E00</t>
+          <t>RCP2_1729D7258E04</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Siopao (Filipino Steamed Buns)</t>
+          <t>Egg Filling For Sushi</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>side</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>flour 416.7 g（3 1/3 cups all-purpose flour）; sugar 100.0 g（1/2 cup white sugar）; salt 3.0 g（1/2 teaspoon salt）; yeast 7.0 g（1 (.25 ounce) package active dry yeast）; water 237.0 g（1 cup lukewarm water）; vegetable_oil 54.5 g（1/4 cup vegetable oil）; vegetable_oil 4.5 g（1 teaspoon vegetable oil, or as needed）</t>
+          <t>egg 100.0 g（2 eggs）; flour 15.6 g（2 tablespoons flour）; sugar 25.0 g（2 tablespoons sugar）; salt 6.1 g（1 teaspoon salt）</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mix flour, sugar, salt, and yeast together in a large bowl. Add water and 1/4 cup oil; mix into a dough. Knead until smooth and elastic, at least 10 minutes. Dust with extra flour if necessary. / Warm up the oven for 1 minute. Turn oven off. / Oil a large bowl; place dough inside and cover with cheesecloth. Place in the warmed oven until size has doubled, about 1 hour. / Punch down dough. Keep in </t>
+          <t>In a bowl beat all ingredients together. / Heat a non stick or lightly oiled pan on a medium heat. I normally use a small frying pan to give me a 1/4 inch thick omelette. / Cook until golden on both sides. / Allow to cool and slice into 1/2 inch thick slices.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>meal_role</t>
+          <t>contains_staple</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>sauce</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>soup / staple / one_bowl / breakfast / snack / dessert / sauce / drink</t>
-        </is>
-      </c>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>RCP2_8F83C05E5E00</t>
+          <t>RCP2_1729D7258E04</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Siopao (Filipino Steamed Buns)</t>
+          <t>Egg Filling For Sushi</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>side</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>flour 416.7 g（3 1/3 cups all-purpose flour）; sugar 100.0 g（1/2 cup white sugar）; salt 3.0 g（1/2 teaspoon salt）; yeast 7.0 g（1 (.25 ounce) package active dry yeast）; water 237.0 g（1 cup lukewarm water）; vegetable_oil 54.5 g（1/4 cup vegetable oil）; vegetable_oil 4.5 g（1 teaspoon vegetable oil, or as needed）</t>
+          <t>egg 100.0 g（2 eggs）; flour 15.6 g（2 tablespoons flour）; sugar 25.0 g（2 tablespoons sugar）; salt 6.1 g（1 teaspoon salt）</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mix flour, sugar, salt, and yeast together in a large bowl. Add water and 1/4 cup oil; mix into a dough. Knead until smooth and elastic, at least 10 minutes. Dust with extra flour if necessary. / Warm up the oven for 1 minute. Turn oven off. / Oil a large bowl; place dough inside and cover with cheesecloth. Place in the warmed oven until size has doubled, about 1 hour. / Punch down dough. Keep in </t>
+          <t>In a bowl beat all ingredients together. / Heat a non stick or lightly oiled pan on a medium heat. I normally use a small frying pan to give me a 1/4 inch thick omelette. / Cook until golden on both sides. / Allow to cool and slice into 1/2 inch thick slices.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>contains_staple</t>
+          <t>protein_sources</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="n"/>
-      <c r="L20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>RCP2_DC882B3F674A</t>
+          <t>RCP2_229B831CE6C7</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Banana Raita With Coconut</t>
+          <t>Mexican Wedding Bells</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>baked_good</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>banana 236.0 g（2 bananas, ripe medium sized peeled and cut into bite size pieces）; lemon_juice 5.2 g（1 teaspoon lemon juice）; yogurt 245.0 g（1 cup plain yogurt）; honey 21.0 g（1 tablespoon honey）; coconut 45.0 g（1/2 cup coconut, desiccated unsweetened）</t>
+          <t>butter 227.0 g（1 c. butter, softened）; powdered_sugar 15.0 g（2 Tbsp. confectioners sugar）; cake_flour 110.0 g（1 c. cake flour）; pecan 119.0 g（1 c. chopped pecans）; vanilla 4.3 g（1 tsp. vanilla）</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Roast/dry fry coconut in a small pan or in a microwave, until a nice aroma rises and it changes colour to slightly brownish pink. You can toast the coconut in a microwave. Spread on a plate and cook on full for 3 (2+1) minutes. Keep aside. / Squeeze a little lemon juice over bananas, to keep them from discolouring. / Mix yogurt with honey and half the coconut. / Add bananas and stir lightly. / Gar</t>
+          <t>Cream together butter and sugar until light and fluffy. / Add flour, pecans and vanilla. / Roll dough into 1-inch balls. / Place on greased sheet pan and flatten slightly. / Bake at 300° for 45 minutes. / Roll in additional confectioners sugar while hot. / When cool, roll in sugar again. / Yields 25 to 30 balls.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1554,45 +1493,40 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>sauce</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>soup / staple / one_bowl / breakfast / snack / dessert / sauce / drink</t>
-        </is>
-      </c>
+          <t>dessert</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="n"/>
-      <c r="L21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>RCP2_DC882B3F674A</t>
+          <t>RCP2_229B831CE6C7</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Banana Raita With Coconut</t>
+          <t>Mexican Wedding Bells</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>baked_good</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>banana 236.0 g（2 bananas, ripe medium sized peeled and cut into bite size pieces）; lemon_juice 5.2 g（1 teaspoon lemon juice）; yogurt 245.0 g（1 cup plain yogurt）; honey 21.0 g（1 tablespoon honey）; coconut 45.0 g（1/2 cup coconut, desiccated unsweetened）</t>
+          <t>butter 227.0 g（1 c. butter, softened）; powdered_sugar 15.0 g（2 Tbsp. confectioners sugar）; cake_flour 110.0 g（1 c. cake flour）; pecan 119.0 g（1 c. chopped pecans）; vanilla 4.3 g（1 tsp. vanilla）</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Roast/dry fry coconut in a small pan or in a microwave, until a nice aroma rises and it changes colour to slightly brownish pink. You can toast the coconut in a microwave. Spread on a plate and cook on full for 3 (2+1) minutes. Keep aside. / Squeeze a little lemon juice over bananas, to keep them from discolouring. / Mix yogurt with honey and half the coconut. / Add bananas and stir lightly. / Gar</t>
+          <t>Cream together butter and sugar until light and fluffy. / Add flour, pecans and vanilla. / Roll dough into 1-inch balls. / Place on greased sheet pan and flatten slightly. / Bake at 300° for 45 minutes. / Roll in additional confectioners sugar while hot. / When cool, roll in sugar again. / Yields 25 to 30 balls.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1605,38 +1539,37 @@
           <t>false</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
+      <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="n"/>
-      <c r="L22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>RCP2_E8D667BA918A</t>
+          <t>RCP2_290971CF4730</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Fake Feta</t>
+          <t>Mexican Wedding Rings</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>baked_good</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>olive_oil 54.0 g（1/4 cup olive oil）; water 59.2 g（1/4 cup water）; red_wine_vinegar 119.5 g（1/2 cup red wine vinegar）; salt 12.2 g（2 teaspoons salt）; basil 0.5 g（1 teaspoon dried basil）; oregano 0.9 g（1/2 teaspoon oregano）; basil 0.2 g（1/2 teaspoon basil）; tofu 453.6 g（1 lb firm tofu）</t>
+          <t>flour 250.0 g（2 c. flour）; sugar 50.0 g（4 Tbsp. sugar）; mixed_nuts 240.0 g（2 c. nuts）; margarine 226.8 g（1/2 lb. oleo）; vanilla 8.7 g（2 tsp. vanilla）</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>In a large bowl, mix together first 7 ingredients. / Marinate the tofu in the mixture for at least an hour. / Enjoy in your favorite recipes.</t>
+          <t>Cream sugar and oleo. / Add flour, vanilla and nuts. / Roll into 1-inch balls. / Bake 20 to 30 minutes at 350°. / Roll in powdered sugar while hot, then again when cool.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1646,45 +1579,40 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>sauce</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>soup / staple / one_bowl / breakfast / snack / dessert / sauce / drink</t>
-        </is>
-      </c>
+          <t>snack</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="n"/>
-      <c r="L23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>RCP2_E8D667BA918A</t>
+          <t>RCP2_290971CF4730</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Fake Feta</t>
+          <t>Mexican Wedding Rings</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>baked_good</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>olive_oil 54.0 g（1/4 cup olive oil）; water 59.2 g（1/4 cup water）; red_wine_vinegar 119.5 g（1/2 cup red wine vinegar）; salt 12.2 g（2 teaspoons salt）; basil 0.5 g（1 teaspoon dried basil）; oregano 0.9 g（1/2 teaspoon oregano）; basil 0.2 g（1/2 teaspoon basil）; tofu 453.6 g（1 lb firm tofu）</t>
+          <t>flour 250.0 g（2 c. flour）; sugar 50.0 g（4 Tbsp. sugar）; mixed_nuts 240.0 g（2 c. nuts）; margarine 226.8 g（1/2 lb. oleo）; vanilla 8.7 g（2 tsp. vanilla）</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>In a large bowl, mix together first 7 ingredients. / Marinate the tofu in the mixture for at least an hour. / Enjoy in your favorite recipes.</t>
+          <t>Cream sugar and oleo. / Add flour, vanilla and nuts. / Roll into 1-inch balls. / Bake 20 to 30 minutes at 350°. / Roll in powdered sugar while hot, then again when cool.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1697,23 +1625,22 @@
           <t>false</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="I24" s="3" t="n"/>
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>RCP2_ED8C37EACE4D</t>
+          <t>RCP2_2E6B4C7D3281</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Mock Feta Cheese ( Vegan Substitute )</t>
+          <t>Granny Gibbs' Famous Dumplings</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1723,12 +1650,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>olive_oil 54.0 g（1/4 cup olive oil）; water 59.2 g（1/4 cup water）; red_wine_vinegar 119.5 g（1/2 cup red wine vinegar）; salt 12.2 g（2 teaspoons salt）; basil 1.5 g（1 tablespoon dried basil）; oregano 0.9 g（1/2 teaspoon dried oregano）; black_pepper 1.1 g（1/2 teaspoon pepper）; tofu 453.6 g（1 lb firm tofu, herb flavored, cubed or crumbled）</t>
+          <t>flour 375.0 g（3 c. flour）; baking_powder 4.6 g（1 tsp. baking powder）; egg 100.0 g（2 eggs）; milk 91.5 g（1/4 to 1/2 c. milk）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Place everything but the tofu in the bowl and whisk together. / Add tofu, stir, and let sit for at least an hour.</t>
+          <t>Sift flour and baking powder. / Add to beaten eggs and milk. Roll and stretch each dumpling before dropping into hot broth, cooking until tender. / Serves 6.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1738,30 +1665,25 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>sauce</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>soup / staple / one_bowl / breakfast / snack / dessert / sauce / drink</t>
-        </is>
-      </c>
+          <t>staple</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>RCP2_ED8C37EACE4D</t>
+          <t>RCP2_2E6B4C7D3281</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Mock Feta Cheese ( Vegan Substitute )</t>
+          <t>Granny Gibbs' Famous Dumplings</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1771,12 +1693,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>olive_oil 54.0 g（1/4 cup olive oil）; water 59.2 g（1/4 cup water）; red_wine_vinegar 119.5 g（1/2 cup red wine vinegar）; salt 12.2 g（2 teaspoons salt）; basil 1.5 g（1 tablespoon dried basil）; oregano 0.9 g（1/2 teaspoon dried oregano）; black_pepper 1.1 g（1/2 teaspoon pepper）; tofu 453.6 g（1 lb firm tofu, herb flavored, cubed or crumbled）</t>
+          <t>flour 375.0 g（3 c. flour）; baking_powder 4.6 g（1 tsp. baking powder）; egg 100.0 g（2 eggs）; milk 91.5 g（1/4 to 1/2 c. milk）</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Place everything but the tofu in the bowl and whisk together. / Add tofu, stir, and let sit for at least an hour.</t>
+          <t>Sift flour and baking powder. / Add to beaten eggs and milk. Roll and stretch each dumpling before dropping into hot broth, cooking until tender. / Serves 6.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1786,74 +1708,68 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="n"/>
       <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>RCP2_F9AC64939A2C</t>
+          <t>RCP2_2E6B4C7D3281</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Welsh Rarebit</t>
+          <t>Granny Gibbs' Famous Dumplings</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>side</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>butter 21.3 g（1 1/2 Tbsp. butter）; flour 11.7 g（1 1/2 Tbsp. flour）; milk 366.0 g（1 1/2 c. milk）; cheddar 113.0 g（1 c. grated Cheddar cheese）; salt 3.0 g（1/2 tsp. salt）; mustard 2.6 g（1/2 tsp. mustard）; paprika 0.3 g（1/8 tsp. paprika）</t>
+          <t>flour 375.0 g（3 c. flour）; baking_powder 4.6 g（1 tsp. baking powder）; egg 100.0 g（2 eggs）; milk 91.5 g（1/4 to 1/2 c. milk）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Make white sauce of butter, flour and milk. / Add cheese and stir over low heat until cheese is melted. / Add seasonings. / Serve hot over buttered toast or crackers.</t>
+          <t>Sift flour and baking powder. / Add to beaten eggs and milk. Roll and stretch each dumpling before dropping into hot broth, cooking until tender. / Serves 6.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>meal_role</t>
+          <t>protein_sources</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>sauce</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>soup / staple / one_bowl / breakfast / snack / dessert / sauce / drink</t>
-        </is>
-      </c>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="n"/>
       <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>RCP2_F9AC64939A2C</t>
+          <t>RCP2_310A97E81CC3</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Welsh Rarebit</t>
+          <t>Taco Baked Potatoes</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1863,148 +1779,141 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>butter 21.3 g（1 1/2 Tbsp. butter）; flour 11.7 g（1 1/2 Tbsp. flour）; milk 366.0 g（1 1/2 c. milk）; cheddar 113.0 g（1 c. grated Cheddar cheese）; salt 3.0 g（1/2 tsp. salt）; mustard 2.6 g（1/2 tsp. mustard）; paprika 0.3 g（1/8 tsp. paprika）</t>
+          <t>potato 852.0 g（4 medium baking potatoes）; yogurt 245.0 g（1 c. plain yogurt）; black_pepper 0.3 g（1/8 tsp. pepper）; cheddar 84.8 g（3/4 c. shredded Cheddar）; green_chili 75.0 g（1/2 c. chopped, well drained green chilies）; pimento 48.0 g（1/4 c. chopped pimentos, well drained）; cilantro 1.0 g（1 Tbsp. chopped cilantro）; lime_juice 15.1 g（1 Tbsp. lime juice）; avocado 150.0 g（1 ripe avocado）</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Make white sauce of butter, flour and milk. / Add cheese and stir over low heat until cheese is melted. / Add seasonings. / Serve hot over buttered toast or crackers.</t>
+          <t>Wash potatoes well. / Bake potatoes at 400° for 1 hour or until soft. / Cut potatoes in half lengthwise, carefully scoop out potato pulp into bowl (leave 1/2-inch pulp to keep potato skin intact). Set skins aside. / Add yogurt and pepper to pulp; mash until fluffy. Stir in 1/2 cup cheese, chilies, pimento and cilantro into mixture. Stuff skins with mixture. / Place stuffed potatoes on ungreased ba</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>contains_staple</t>
+          <t>meal_role</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
+          <t>staple</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="n"/>
       <c r="J28" s="3" t="n"/>
       <c r="K28" s="3" t="n"/>
-      <c r="L28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>RCP2_290971CF4730</t>
+          <t>RCP2_310A97E81CC3</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Mexican Wedding Rings</t>
+          <t>Taco Baked Potatoes</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>baked_good</t>
+          <t>main</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>flour 250.0 g（2 c. flour）; sugar 50.0 g（4 Tbsp. sugar）; mixed_nuts 240.0 g（2 c. nuts）; margarine 226.8 g（1/2 lb. oleo）; vanilla 8.7 g（2 tsp. vanilla）</t>
+          <t>potato 852.0 g（4 medium baking potatoes）; yogurt 245.0 g（1 c. plain yogurt）; black_pepper 0.3 g（1/8 tsp. pepper）; cheddar 84.8 g（3/4 c. shredded Cheddar）; green_chili 75.0 g（1/2 c. chopped, well drained green chilies）; pimento 48.0 g（1/4 c. chopped pimentos, well drained）; cilantro 1.0 g（1 Tbsp. chopped cilantro）; lime_juice 15.1 g（1 Tbsp. lime juice）; avocado 150.0 g（1 ripe avocado）</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Cream sugar and oleo. / Add flour, vanilla and nuts. / Roll into 1-inch balls. / Bake 20 to 30 minutes at 350°. / Roll in powdered sugar while hot, then again when cool.</t>
+          <t>Wash potatoes well. / Bake potatoes at 400° for 1 hour or until soft. / Cut potatoes in half lengthwise, carefully scoop out potato pulp into bowl (leave 1/2-inch pulp to keep potato skin intact). Set skins aside. / Add yogurt and pepper to pulp; mash until fluffy. Stir in 1/2 cup cheese, chilies, pimento and cilantro into mixture. Stuff skins with mixture. / Place stuffed potatoes on ungreased ba</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>meal_role</t>
+          <t>contains_staple</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>snack</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>one_bowl / breakfast / snack / dessert</t>
-        </is>
-      </c>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="n"/>
       <c r="J29" s="3" t="n"/>
       <c r="K29" s="3" t="n"/>
-      <c r="L29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>RCP2_290971CF4730</t>
+          <t>RCP2_355D74D12F4C</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Mexican Wedding Rings</t>
+          <t>Vietnamese Spiced Paté</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>baked_good</t>
+          <t>snack_appetizer</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>flour 250.0 g（2 c. flour）; sugar 50.0 g（4 Tbsp. sugar）; mixed_nuts 240.0 g（2 c. nuts）; margarine 226.8 g（1/2 lb. oleo）; vanilla 8.7 g（2 tsp. vanilla）</t>
+          <t>pork 453.6 g（1 pound ground pork shoulder or butt）; liver 453.6 g（1 pound chicken liver）; pork_fatback 680.4 g（1 1/2 pounds pork fat back）; bacon 420.0 g（15 pieces raw bacon）; garlic 6.0 g（2 cloves crushed garlic）; shallot 80.0 g（2 large minced shallots）; egg 50.0 g（1 whole egg）; egg_yolk 17.0 g（1 egg yolk）; fish_sauce 27.0 g（1 1/2 tablespoons fish sauce）; brandy 21.1 g（1 1/2 tablespoons cognac）; cinnamon 1.3 g（1/2 teaspoon cinnamon）; cumin 1.1 g（1/2 teaspoon fresh ground cumin）; coriander 0.5 g（1/2 teaspoon ground coriander）; cloves_spice 0.2 g（1 pinch ground cloves）; allspice 0.2 g（1 pinch ground allspice）; nutmeg 0.2 g（1 pinch fresh ground nutmeg）; salt 12.2 g（2 teaspoons salt）; black_pepper 2.3 g（1 teaspoon fresh ground black pepper）</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Cream sugar and oleo. / Add flour, vanilla and nuts. / Roll into 1-inch balls. / Bake 20 to 30 minutes at 350°. / Roll in powdered sugar while hot, then again when cool.</t>
+          <t>Clean livers by placing on a cutting board and holding onto the sinewy parts. Using the back of a knife scrape the meaty part gently away from the sinew. You will see the webs of sinew and be able to discard them. / (skip this step if using pre-ground spices) If you can use fresh spices grind them together with a mortar and pestle or coffee grinder. / Grind together the chopped liver, pork, fat ba</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>contains_staple</t>
+          <t>protein_sources</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
+          <t>chicken,pork</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="n"/>
       <c r="J30" s="3" t="n"/>
       <c r="K30" s="3" t="n"/>
-      <c r="L30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>RCP2_49CA27EAC641</t>
+          <t>RCP2_3CC1354BC571</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Alfajores De Maizena</t>
+          <t>Brazilian Arroz De Festa (Confetti Rice)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>baked_good</t>
+          <t>side</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>cornstarch 320.0 g（2 1/2 cups cornstarch (Maizena Brand)）; flour 208.3 g（1 2/3 cups flour）; baking_soda 2.3 g（1/2 teaspoon baking soda）; baking_powder 9.2 g（2 teaspoons baking powder）; sugar 150.0 g（3/4 cup sugar）; butter 227.0 g（1 cup butter）; egg_yolk 51.0 g（3 egg yolks）; vanilla 13.0 g（1 tablespoon vanilla extract）; lemon_zest 3.0 g（1 -2 teaspoon lemon zest (or powdered lemon)）</t>
+          <t>vegetable_oil 34.1 g（2 1/2 tablespoons vegetable oil）; onion 40.0 g（1/4 cup minced onion）; garlic 9.0 g（3 large cloves garlic, minced）; rice 370.0 g（2 cups basmati rice, rinsed and drained）; salt 6.1 g（1 teaspoon salt）; water 948.0 g（4 cups hot water）; carrot 122.0 g（2 carrots, peeled and chopped）; bell_pepper 120.0 g（1 green bell pepper, chopped）; bell_pepper 120.0 g（1 red bell pepper, chopped）; corn 432.3 g（1 (15.25 ounce) can whole kernel corn, drained）; butter 28.4 g（2 tablespoons butter, divided (optional)）; raisin 72.5 g（1/2 cup raisins）; cranberry 50.0 g（1/2 cup dried cranberries）; raisin 36.2 g（1/4 cup golden raisins）</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Beat the butter until creamy. Add the sugar gradually, beating until the mixture is light and fluffy. Add egg yolks, one at a time, beating well after each addition. Beat in the vanilla and lemon rind. / Sift together the cornstarch, flour, baking powder and soda. Gradually add the dry ingredients to the butter mixture, beating until thoroughly combined. / Drop the batter by small spoonfuls onto w</t>
+          <t>Heat oil in a saucepan over medium heat. Cook and stir onion for 1 minute. Add garlic; cook until golden brown, about 1 minute. Add rice and salt; cook rice until it starts to brown, 3 to 5 minutes. Pour in hot water. Reduce heat to low, cover, and simmer until water has been absorbed, 20 to 25 minutes. / Place carrots in a saucepan with enough water to cover. Cook over medium-high heat for 5 minu</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2014,45 +1923,40 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>snack</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>one_bowl / breakfast / snack / dessert</t>
-        </is>
-      </c>
+          <t>staple</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="n"/>
       <c r="J31" s="3" t="n"/>
       <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>RCP2_49CA27EAC641</t>
+          <t>RCP2_3CC1354BC571</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Alfajores De Maizena</t>
+          <t>Brazilian Arroz De Festa (Confetti Rice)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>baked_good</t>
+          <t>side</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>cornstarch 320.0 g（2 1/2 cups cornstarch (Maizena Brand)）; flour 208.3 g（1 2/3 cups flour）; baking_soda 2.3 g（1/2 teaspoon baking soda）; baking_powder 9.2 g（2 teaspoons baking powder）; sugar 150.0 g（3/4 cup sugar）; butter 227.0 g（1 cup butter）; egg_yolk 51.0 g（3 egg yolks）; vanilla 13.0 g（1 tablespoon vanilla extract）; lemon_zest 3.0 g（1 -2 teaspoon lemon zest (or powdered lemon)）</t>
+          <t>vegetable_oil 34.1 g（2 1/2 tablespoons vegetable oil）; onion 40.0 g（1/4 cup minced onion）; garlic 9.0 g（3 large cloves garlic, minced）; rice 370.0 g（2 cups basmati rice, rinsed and drained）; salt 6.1 g（1 teaspoon salt）; water 948.0 g（4 cups hot water）; carrot 122.0 g（2 carrots, peeled and chopped）; bell_pepper 120.0 g（1 green bell pepper, chopped）; bell_pepper 120.0 g（1 red bell pepper, chopped）; corn 432.3 g（1 (15.25 ounce) can whole kernel corn, drained）; butter 28.4 g（2 tablespoons butter, divided (optional)）; raisin 72.5 g（1/2 cup raisins）; cranberry 50.0 g（1/2 cup dried cranberries）; raisin 36.2 g（1/4 cup golden raisins）</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Beat the butter until creamy. Add the sugar gradually, beating until the mixture is light and fluffy. Add egg yolks, one at a time, beating well after each addition. Beat in the vanilla and lemon rind. / Sift together the cornstarch, flour, baking powder and soda. Gradually add the dry ingredients to the butter mixture, beating until thoroughly combined. / Drop the batter by small spoonfuls onto w</t>
+          <t>Heat oil in a saucepan over medium heat. Cook and stir onion for 1 minute. Add garlic; cook until golden brown, about 1 minute. Add rice and salt; cook rice until it starts to brown, 3 to 5 minutes. Pour in hot water. Reduce heat to low, cover, and simmer until water has been absorbed, 20 to 25 minutes. / Place carrots in a saucepan with enough water to cover. Cook over medium-high heat for 5 minu</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2062,26 +1966,25 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="n"/>
       <c r="J32" s="3" t="n"/>
       <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>RCP2_59209F8AE7D0</t>
+          <t>RCP2_409262770DBA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>South African Vetkoek</t>
+          <t>Popovers(Portuguese)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2091,12 +1994,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>cake_flour 116.2 g（250 ml cake flour）; baking_powder 4.6 g（1 teaspoon baking powder）; salt 3.0 g（1/2 teaspoon salt）; egg 50.0 g（1 egg）; milk 128.9 g（125 ml milk）; vegetable_oil 115.2 g（125 ml oil (for frying)）</t>
+          <t>flour 125.0 g（1 c. sifted flour）; milk 244.0 g（1 c. milk）; salt 3.0 g（1/2 tsp. salt）; egg 100.0 g（2 eggs）</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Sift flour, baking powder and salt together. / Beat egg separately and add to flour. / Add milk and mix until smooth. / Heat oil in frying pan and drop a heaped tablespoon of the mixture into oil. (Once you have tried this you can decide to use more batter to yield a larger "vetkoek"). / Don't make more than four at a time! / Fry for two to three minutes on one side, then turn and fry for one minu</t>
+          <t>Beat together ingredients with rotary beater just until smooth. / Pour into well-greased deep muffin cup (3/4 full) or oven glass cups (1/2 full). Bake at 425° for 35 to 45 minutes.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2106,30 +2009,25 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>snack</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>protein_main / staple / one_bowl / breakfast / snack / dessert</t>
-        </is>
-      </c>
+          <t>staple</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="n"/>
-      <c r="L33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>RCP2_59209F8AE7D0</t>
+          <t>RCP2_409262770DBA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>South African Vetkoek</t>
+          <t>Popovers(Portuguese)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2139,12 +2037,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>cake_flour 116.2 g（250 ml cake flour）; baking_powder 4.6 g（1 teaspoon baking powder）; salt 3.0 g（1/2 teaspoon salt）; egg 50.0 g（1 egg）; milk 128.9 g（125 ml milk）; vegetable_oil 115.2 g（125 ml oil (for frying)）</t>
+          <t>flour 125.0 g（1 c. sifted flour）; milk 244.0 g（1 c. milk）; salt 3.0 g（1/2 tsp. salt）; egg 100.0 g（2 eggs）</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Sift flour, baking powder and salt together. / Beat egg separately and add to flour. / Add milk and mix until smooth. / Heat oil in frying pan and drop a heaped tablespoon of the mixture into oil. (Once you have tried this you can decide to use more batter to yield a larger "vetkoek"). / Don't make more than four at a time! / Fry for two to three minutes on one side, then turn and fry for one minu</t>
+          <t>Beat together ingredients with rotary beater just until smooth. / Pour into well-greased deep muffin cup (3/4 full) or oven glass cups (1/2 full). Bake at 425° for 35 to 45 minutes.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2154,61 +2052,56 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="n"/>
       <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="n"/>
-      <c r="L34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>RCP2_5954131C04AC</t>
+          <t>RCP2_441BD2095B93</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Scrumpets</t>
+          <t>Vietnamese Pâté Chaud</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>baked_good</t>
+          <t>snack_appetizer</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>flour 500.0 g（4 cups all-purpose flour, sifted）; sugar 25.0 g（2 tablespoons white sugar）; baking_powder 18.3 g（4 teaspoons baking powder）; salt 6.1 g（1 teaspoon salt）; milk 244.0 g（1 cup milk）; egg 150.0 g（3 eggs）; butter 113.5 g（1/2 cup butter, melted）; butter 4.7 g（1 teaspoon butter, or as needed (optional)）</t>
+          <t>pork 300.0 g（300 grams ground pork）; pate 75.0 g（75 grams pate）; onion 110.0 g（1 yellow onion, finely diced）; salt 3.0 g（1/2 teaspoon salt (or more to taste)）; black_pepper 1.1 g（1/2 teaspoon ground black pepper）; sugar 1.0 g（1/4 teaspoon sugar）; potato_starch 8.0 g（2 teaspoons potato starch）; puff_pastry 490.0 g（2 sheets of puff pastry）; egg 50.0 g（1 egg beaten）</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Place flour, sugar, baking powder, and salt in a bowl and mix well. / Beat milk, eggs, and melted butter together in another bowl; stir into the flour mixture with a few strokes. Handle dough as little as possible. / Scrape the dough out onto a generously floured surface. Dip your fingers in flour and pat dough into a circle about 1/2-inch thick. Cut into 4-inch rounds to form the scrumpets. / Mel</t>
+          <t>Filling: Combine the pork, pate, onion, potato starch and season with salt, sugar and pepper. Mix thoroughly until all of the ingredients are uniformly amalgamated. To ensure that the mixture is properly seasoned, add the salt gradually and taste after each addition by cooking a spoonful in the microwave (but without the spoon). / Preheat oven to 175°C.
+Work with one pastry sheet at time, leaving</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>meal_role</t>
+          <t>protein_sources</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>snack</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>protein_main / staple / one_bowl / breakfast / snack / dessert</t>
-        </is>
-      </c>
+          <t>pork</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="n"/>
       <c r="J35" s="3" t="n"/>
       <c r="K35" s="3" t="n"/>
-      <c r="L35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2216,12 +2109,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>RCP2_5954131C04AC</t>
+          <t>RCP2_44C42897EBAD</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Scrumpets</t>
+          <t>Peruvian Alfajores</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2231,41 +2124,40 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>flour 500.0 g（4 cups all-purpose flour, sifted）; sugar 25.0 g（2 tablespoons white sugar）; baking_powder 18.3 g（4 teaspoons baking powder）; salt 6.1 g（1 teaspoon salt）; milk 244.0 g（1 cup milk）; egg 150.0 g（3 eggs）; butter 113.5 g（1/2 cup butter, melted）; butter 4.7 g（1 teaspoon butter, or as needed (optional)）</t>
+          <t>flour 250.0 g（2 cups all-purpose flour）; powdered_sugar 30.0 g（1/4 cup confectioners' sugar）; shortening 153.8 g（3/4 cup vegetable shortening, chilled）; caramel 80.0 g（1/4 cup dulce de leche）; powdered_sugar 15.0 g（Confectioners' sugar）</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Place flour, sugar, baking powder, and salt in a bowl and mix well. / Beat milk, eggs, and melted butter together in another bowl; stir into the flour mixture with a few strokes. Handle dough as little as possible. / Scrape the dough out onto a generously floured surface. Dip your fingers in flour and pat dough into a circle about 1/2-inch thick. Cut into 4-inch rounds to form the scrumpets. / Mel</t>
+          <t>Preheat oven to 350 degrees F (175 degrees C). / Sift flour and 1/4 cup confectioners' sugar together into a bowl. Rub the shortening into the flour until completely incorporated to form a dough. Roll out on a floured surface to 1/4-inch thick, then cut into 1 to 1 1/2-inch circles with a small, round cookie cutter. Place circles onto an ungreased baking sheet, and poke each twice with a fork. / B</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>contains_staple</t>
+          <t>meal_role</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
+          <t>dessert</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="n"/>
       <c r="J36" s="3" t="n"/>
       <c r="K36" s="3" t="n"/>
-      <c r="L36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>RCP2_81C30294D91B</t>
+          <t>RCP2_44C42897EBAD</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Turkish Pogaca</t>
+          <t>Peruvian Alfajores</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2275,32 +2167,27 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>flour 600.0 g（600 g flour）; milk 309.4 g（300 ml nonfat milk）; sugar 10.0 g（10 g sugar）; yeast 7.1 g（1/4 ounce yeast）; vegetable_oil 161.3 g（175 ml vegetable oil）; egg 50.0 g（1 egg）; egg_yolk 17.0 g（1 egg yolk）; salt 6.1 g（1 teaspoon salt）; poppy_seed 9.0 g（1 tablespoon poppy seed）; feta 150.0 g（1 cup feta cheese）; parsley 60.0 g（1 cup parsley）</t>
+          <t>flour 250.0 g（2 cups all-purpose flour）; powdered_sugar 30.0 g（1/4 cup confectioners' sugar）; shortening 153.8 g（3/4 cup vegetable shortening, chilled）; caramel 80.0 g（1/4 cup dulce de leche）; powdered_sugar 15.0 g（Confectioners' sugar）</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Mix everything together except the egg yolk. / Wait for 1 hour for batter to double. / Make small rounds as big as half of your palm. / Press it with your fingers to make it as big as your palm. / Mix feta cheese and parsley. / Put the mixture into these small rounds and close it and round it again. / Place it on the oiled oven sheet. / Brush all the batch with the egg yolk. / Place it in the preh</t>
+          <t>Preheat oven to 350 degrees F (175 degrees C). / Sift flour and 1/4 cup confectioners' sugar together into a bowl. Rub the shortening into the flour until completely incorporated to form a dough. Roll out on a floured surface to 1/4-inch thick, then cut into 1 to 1 1/2-inch circles with a small, round cookie cutter. Place circles onto an ungreased baking sheet, and poke each twice with a fork. / B</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>meal_role</t>
+          <t>contains_staple</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>snack</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>staple / one_bowl / breakfast / snack / dessert</t>
-        </is>
-      </c>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="n"/>
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="n"/>
-      <c r="L37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2308,91 +2195,85 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>RCP2_81C30294D91B</t>
+          <t>RCP2_45BE0219D45D</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Turkish Pogaca</t>
+          <t>Heart-Shaped Tamagoyaki (Japanese Omelet)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>baked_good</t>
+          <t>side</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>flour 600.0 g（600 g flour）; milk 309.4 g（300 ml nonfat milk）; sugar 10.0 g（10 g sugar）; yeast 7.1 g（1/4 ounce yeast）; vegetable_oil 161.3 g（175 ml vegetable oil）; egg 50.0 g（1 egg）; egg_yolk 17.0 g（1 egg yolk）; salt 6.1 g（1 teaspoon salt）; poppy_seed 9.0 g（1 tablespoon poppy seed）; feta 150.0 g（1 cup feta cheese）; parsley 60.0 g（1 cup parsley）</t>
+          <t>vegetable_oil 13.6 g（1 tablespoon vegetable oil）; egg 150.0 g（3 large eggs）; salt 1.5 g（1/4 teaspoon salt）; sesame_oil 2.3 g（1/2 teaspoon toasted sesame oil）; mirin 5.6 g（1 teaspoon mirin）</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Mix everything together except the egg yolk. / Wait for 1 hour for batter to double. / Make small rounds as big as half of your palm. / Press it with your fingers to make it as big as your palm. / Mix feta cheese and parsley. / Put the mixture into these small rounds and close it and round it again. / Place it on the oiled oven sheet. / Brush all the batch with the egg yolk. / Place it in the preh</t>
+          <t xml:space="preserve">Pour the oil into a small bowl. Dip a folded up piece of paper towel in the oil and use it to apply a film of oil to a nonstick skillet about 8" in diameter. Heat the pan on medium heat. / Scramble the rest of the ingredients together, but try not to introduce too many air bubbles into the mixture. / Pour a third of the egg mixture onto the hot pan and swirl it around so that the bottom is evenly </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>contains_staple</t>
+          <t>meal_role</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
+          <t>protein_main</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="n"/>
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="n"/>
-      <c r="L38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>RCP2_A887D44E2FC0</t>
+          <t>RCP2_45BE0219D45D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Sauerkraut pierogii</t>
+          <t>Heart-Shaped Tamagoyaki (Japanese Omelet)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>side</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>sunflower_oil 13.6 g（1 tablespoon Sunflower Oil）; shallot 80.0 g（2 chopped Shallots）; sauerkraut 150.0 g（150g Sauerkraut）; cabbage 150.0 g（150g Hispi (sweetheart) Cabbage）; egg 50.0 g（1 beaten Egg）; vegetable_oil 6.8 g（1/2 tbs Vegetable Oil）; flour 350.0 g（350g Plain Flour）; vegetable_oil 230.4 g（For frying Vegetable Oil）; shallot 80.0 g（2 sliced Shallots）; flour 15.6 g（Dusting Plain Flour）; butter 45.0 g（45g Butter）; sour_cream 58.3 g（60 ml Sour Cream）</t>
+          <t>vegetable_oil 13.6 g（1 tablespoon vegetable oil）; egg 150.0 g（3 large eggs）; salt 1.5 g（1/4 teaspoon salt）; sesame_oil 2.3 g（1/2 teaspoon toasted sesame oil）; mirin 5.6 g（1 teaspoon mirin）</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>First, make the crispy shallots. Heat the oil in a saucepan to 180C (a cube of bread will turn golden in 15 secs). Toss the shallots in a little flour and deep-fry for 1 min or until light golden and crispy. Drain on kitchen paper. Can be made up to two days before and kept in an airtight container. / To make the filling, heat the oil in a medium non-stick frying pan and gently fry the shallots fo</t>
+          <t xml:space="preserve">Pour the oil into a small bowl. Dip a folded up piece of paper towel in the oil and use it to apply a film of oil to a nonstick skillet about 8" in diameter. Heat the pan on medium heat. / Scramble the rest of the ingredients together, but try not to introduce too many air bubbles into the mixture. / Pour a third of the egg mixture onto the hot pan and swirl it around so that the bottom is evenly </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>meal_role</t>
+          <t>contains_staple</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>snack</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>soup / staple / one_bowl / breakfast / snack / dessert / sauce / drink</t>
-        </is>
-      </c>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -2400,91 +2281,85 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>RCP2_A887D44E2FC0</t>
+          <t>RCP2_49CA27EAC641</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Sauerkraut pierogii</t>
+          <t>Alfajores De Maizena</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>baked_good</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>sunflower_oil 13.6 g（1 tablespoon Sunflower Oil）; shallot 80.0 g（2 chopped Shallots）; sauerkraut 150.0 g（150g Sauerkraut）; cabbage 150.0 g（150g Hispi (sweetheart) Cabbage）; egg 50.0 g（1 beaten Egg）; vegetable_oil 6.8 g（1/2 tbs Vegetable Oil）; flour 350.0 g（350g Plain Flour）; vegetable_oil 230.4 g（For frying Vegetable Oil）; shallot 80.0 g（2 sliced Shallots）; flour 15.6 g（Dusting Plain Flour）; butter 45.0 g（45g Butter）; sour_cream 58.3 g（60 ml Sour Cream）</t>
+          <t>cornstarch 320.0 g（2 1/2 cups cornstarch (Maizena Brand)）; flour 208.3 g（1 2/3 cups flour）; baking_soda 2.3 g（1/2 teaspoon baking soda）; baking_powder 9.2 g（2 teaspoons baking powder）; sugar 150.0 g（3/4 cup sugar）; butter 227.0 g（1 cup butter）; egg_yolk 51.0 g（3 egg yolks）; vanilla 13.0 g（1 tablespoon vanilla extract）; lemon_zest 3.0 g（1 -2 teaspoon lemon zest (or powdered lemon)）</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>First, make the crispy shallots. Heat the oil in a saucepan to 180C (a cube of bread will turn golden in 15 secs). Toss the shallots in a little flour and deep-fry for 1 min or until light golden and crispy. Drain on kitchen paper. Can be made up to two days before and kept in an airtight container. / To make the filling, heat the oil in a medium non-stick frying pan and gently fry the shallots fo</t>
+          <t>Beat the butter until creamy. Add the sugar gradually, beating until the mixture is light and fluffy. Add egg yolks, one at a time, beating well after each addition. Beat in the vanilla and lemon rind. / Sift together the cornstarch, flour, baking powder and soda. Gradually add the dry ingredients to the butter mixture, beating until thoroughly combined. / Drop the batter by small spoonfuls onto w</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>contains_staple</t>
+          <t>meal_role</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
+          <t>snack</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="n"/>
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="n"/>
-      <c r="L40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>RCP2_806075FC7BF8</t>
+          <t>RCP2_49CA27EAC641</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>French Onion Soup</t>
+          <t>Alfajores De Maizena</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>soup</t>
+          <t>baked_good</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>onion 453.6 g（1 lb. yellow onions, sliced）; butter 56.8 g（1/4 c. butter）; flour 15.6 g（2 Tbsp. flour）; water 948.0 g（4 c. water）; bouillon 20.0 g（5 beef bouillon cubes）; salt 3.0 g（1/2 tsp. salt）; bread 116.0 g（4 slices French bread, toasted）; parmesan 50.0 g（1/2 c. Parmesan cheese）</t>
+          <t>cornstarch 320.0 g（2 1/2 cups cornstarch (Maizena Brand)）; flour 208.3 g（1 2/3 cups flour）; baking_soda 2.3 g（1/2 teaspoon baking soda）; baking_powder 9.2 g（2 teaspoons baking powder）; sugar 150.0 g（3/4 cup sugar）; butter 227.0 g（1 cup butter）; egg_yolk 51.0 g（3 egg yolks）; vanilla 13.0 g（1 tablespoon vanilla extract）; lemon_zest 3.0 g（1 -2 teaspoon lemon zest (or powdered lemon)）</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Saute onions in butter in heavy saucepan. / Stir in flour. Cook until flour is lightly browned. / Add water, bouillon and salt. / Bring to a boil, stirring to dissolve bouillon. / Simmer, covered, for 15 minutes. / Ladle into ovenproof bowls. / Top with French bread. / Sprinkle with cheese. / Broil until cheese is light brown. / Yield: 4 servings.</t>
+          <t>Beat the butter until creamy. Add the sugar gradually, beating until the mixture is light and fluffy. Add egg yolks, one at a time, beating well after each addition. Beat in the vanilla and lemon rind. / Sift together the cornstarch, flour, baking powder and soda. Gradually add the dry ingredients to the butter mixture, beating until thoroughly combined. / Drop the batter by small spoonfuls onto w</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>meal_role</t>
+          <t>contains_staple</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>soup</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>soup / one_bowl</t>
-        </is>
-      </c>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="n"/>
-      <c r="L41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -2492,91 +2367,85 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>RCP2_806075FC7BF8</t>
+          <t>RCP2_50567B7B0B2C</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>French Onion Soup</t>
+          <t>Kumpir</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>soup</t>
+          <t>main</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>onion 453.6 g（1 lb. yellow onions, sliced）; butter 56.8 g（1/4 c. butter）; flour 15.6 g（2 Tbsp. flour）; water 948.0 g（4 c. water）; bouillon 20.0 g（5 beef bouillon cubes）; salt 3.0 g（1/2 tsp. salt）; bread 116.0 g（4 slices French bread, toasted）; parmesan 50.0 g（1/2 c. Parmesan cheese）</t>
+          <t>potato 426.0 g（2 large Potatoes）; butter 28.4 g（2 tbs Butter）; cheese 150.0 g（150g Cheese）; onion 110.0 g（1 large Onion）; bell_pepper 120.0 g（1 large Red Pepper）; cayenne 0.2 g（Pinch Red Chilli Flakes）</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Saute onions in butter in heavy saucepan. / Stir in flour. Cook until flour is lightly browned. / Add water, bouillon and salt. / Bring to a boil, stirring to dissolve bouillon. / Simmer, covered, for 15 minutes. / Ladle into ovenproof bowls. / Top with French bread. / Sprinkle with cheese. / Broil until cheese is light brown. / Yield: 4 servings.</t>
+          <t>If you order kumpir in Turkey, the standard filling is first, lots of butter mashed into the potato, followed by cheese. There’s then a row of other toppings that you can just point at to your heart’s content – sweetcorn, olives, salami, coleslaw, Russian salad, allsorts – and you walk away with an over-stuffed potato because you got ever-excited by the choices on offer. / Grate (roughly – you can</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>contains_staple</t>
+          <t>meal_role</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
+          <t>staple</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="n"/>
       <c r="K42" s="3" t="n"/>
-      <c r="L42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>RCP2_EAAD839F9258</t>
+          <t>RCP2_50567B7B0B2C</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Mushroom-Barley Soup</t>
+          <t>Kumpir</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>soup</t>
+          <t>main</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>onion 99.2 g（3 1/2 oz. onions, chopped）; celery 99.2 g（3 1/2 oz. celery, chopped）; garlic 3.0 g（1 clove garlic, minced）; butter 56.8 g（4 Tbsp. butter）; barley 70.9 g（2 1/2 oz. barley）; chicken_broth 1892.8 g（2 qt. chicken stock）; mushroom 368.5 g（13 oz. fresh mushrooms, sauteed in 1/4 c. butter）</t>
+          <t>potato 426.0 g（2 large Potatoes）; butter 28.4 g（2 tbs Butter）; cheese 150.0 g（150g Cheese）; onion 110.0 g（1 large Onion）; bell_pepper 120.0 g（1 large Red Pepper）; cayenne 0.2 g（Pinch Red Chilli Flakes）</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Saute onions, celery and garlic in butter until tender. / Add dry barley and saute 10 more minutes until barley gets thick. Add chicken stock and mushrooms. Boil and simmer until barley is tender, about 1/2 hour to 45 minutes. Serves 6.</t>
+          <t>If you order kumpir in Turkey, the standard filling is first, lots of butter mashed into the potato, followed by cheese. There’s then a row of other toppings that you can just point at to your heart’s content – sweetcorn, olives, salami, coleslaw, Russian salad, allsorts – and you walk away with an over-stuffed potato because you got ever-excited by the choices on offer. / Grate (roughly – you can</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>meal_role</t>
+          <t>contains_staple</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>soup</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>soup / one_bowl</t>
-        </is>
-      </c>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="n"/>
       <c r="J43" s="3" t="n"/>
       <c r="K43" s="3" t="n"/>
-      <c r="L43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -2584,91 +2453,85 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>RCP2_EAAD839F9258</t>
+          <t>RCP2_59209F8AE7D0</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Mushroom-Barley Soup</t>
+          <t>South African Vetkoek</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>soup</t>
+          <t>baked_good</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>onion 99.2 g（3 1/2 oz. onions, chopped）; celery 99.2 g（3 1/2 oz. celery, chopped）; garlic 3.0 g（1 clove garlic, minced）; butter 56.8 g（4 Tbsp. butter）; barley 70.9 g（2 1/2 oz. barley）; chicken_broth 1892.8 g（2 qt. chicken stock）; mushroom 368.5 g（13 oz. fresh mushrooms, sauteed in 1/4 c. butter）</t>
+          <t>cake_flour 116.2 g（250 ml cake flour）; baking_powder 4.6 g（1 teaspoon baking powder）; salt 3.0 g（1/2 teaspoon salt）; egg 50.0 g（1 egg）; milk 128.9 g（125 ml milk）; vegetable_oil 115.2 g（125 ml oil (for frying)）</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Saute onions, celery and garlic in butter until tender. / Add dry barley and saute 10 more minutes until barley gets thick. Add chicken stock and mushrooms. Boil and simmer until barley is tender, about 1/2 hour to 45 minutes. Serves 6.</t>
+          <t>Sift flour, baking powder and salt together. / Beat egg separately and add to flour. / Add milk and mix until smooth. / Heat oil in frying pan and drop a heaped tablespoon of the mixture into oil. (Once you have tried this you can decide to use more batter to yield a larger "vetkoek"). / Don't make more than four at a time! / Fry for two to three minutes on one side, then turn and fry for one minu</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>contains_staple</t>
+          <t>meal_role</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
+          <t>snack</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="n"/>
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="n"/>
-      <c r="L44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>RCP2_F0A2E3140892</t>
+          <t>RCP2_59209F8AE7D0</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Hearty French Onion Soup</t>
+          <t>South African Vetkoek</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>soup</t>
+          <t>baked_good</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>butter 56.8 g（1/4 c. butter）; onion 550.0 g（5 medium yellow onions, thinly sliced）; sugar 0.5 g（1/8 tsp. sugar）; flour 15.6 g（2 Tbsp. flour）; beef_broth 1200.0 g（5 c. low sodium beef broth）; thyme 0.3 g（1/2 tsp. thyme, crumbled）; bay_leaf 0.2 g（1 bay leaf）; black_pepper 0.6 g（1/4 tsp. pepper）; bread 232.0 g（8 (1/2-inch) slices French bread, toasted）; swiss_cheese 108.0 g（1 c. shredded Swiss cheese）; parmesan 25.0 g（1/4 c. Parmesan cheese）</t>
+          <t>cake_flour 116.2 g（250 ml cake flour）; baking_powder 4.6 g（1 teaspoon baking powder）; salt 3.0 g（1/2 teaspoon salt）; egg 50.0 g（1 egg）; milk 128.9 g（125 ml milk）; vegetable_oil 115.2 g（125 ml oil (for frying)）</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melt butter in large saucepan over medium heat. / Add onions. Cook for 10 to 15 minutes or until golden, stirring gently. / Stir in sugar and flour. / Cook for 3 minutes longer, stirring constantly. / Add broth, thyme, bay leaf and pepper; mix well. Bring to a boil over medium-high heat, stirring constantly. / Boil for 6 minutes, stirring constantly; reduce heat. / Simmer, loosely covered, for 30 </t>
+          <t>Sift flour, baking powder and salt together. / Beat egg separately and add to flour. / Add milk and mix until smooth. / Heat oil in frying pan and drop a heaped tablespoon of the mixture into oil. (Once you have tried this you can decide to use more batter to yield a larger "vetkoek"). / Don't make more than four at a time! / Fry for two to three minutes on one side, then turn and fry for one minu</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>meal_role</t>
+          <t>contains_staple</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>soup</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>soup / one_bowl</t>
-        </is>
-      </c>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="n"/>
       <c r="J45" s="3" t="n"/>
       <c r="K45" s="3" t="n"/>
-      <c r="L45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -2676,91 +2539,85 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>RCP2_F0A2E3140892</t>
+          <t>RCP2_5954131C04AC</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Hearty French Onion Soup</t>
+          <t>Scrumpets</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>soup</t>
+          <t>baked_good</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>butter 56.8 g（1/4 c. butter）; onion 550.0 g（5 medium yellow onions, thinly sliced）; sugar 0.5 g（1/8 tsp. sugar）; flour 15.6 g（2 Tbsp. flour）; beef_broth 1200.0 g（5 c. low sodium beef broth）; thyme 0.3 g（1/2 tsp. thyme, crumbled）; bay_leaf 0.2 g（1 bay leaf）; black_pepper 0.6 g（1/4 tsp. pepper）; bread 232.0 g（8 (1/2-inch) slices French bread, toasted）; swiss_cheese 108.0 g（1 c. shredded Swiss cheese）; parmesan 25.0 g（1/4 c. Parmesan cheese）</t>
+          <t>flour 500.0 g（4 cups all-purpose flour, sifted）; sugar 25.0 g（2 tablespoons white sugar）; baking_powder 18.3 g（4 teaspoons baking powder）; salt 6.1 g（1 teaspoon salt）; milk 244.0 g（1 cup milk）; egg 150.0 g（3 eggs）; butter 113.5 g（1/2 cup butter, melted）; butter 4.7 g（1 teaspoon butter, or as needed (optional)）</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melt butter in large saucepan over medium heat. / Add onions. Cook for 10 to 15 minutes or until golden, stirring gently. / Stir in sugar and flour. / Cook for 3 minutes longer, stirring constantly. / Add broth, thyme, bay leaf and pepper; mix well. Bring to a boil over medium-high heat, stirring constantly. / Boil for 6 minutes, stirring constantly; reduce heat. / Simmer, loosely covered, for 30 </t>
+          <t>Place flour, sugar, baking powder, and salt in a bowl and mix well. / Beat milk, eggs, and melted butter together in another bowl; stir into the flour mixture with a few strokes. Handle dough as little as possible. / Scrape the dough out onto a generously floured surface. Dip your fingers in flour and pat dough into a circle about 1/2-inch thick. Cut into 4-inch rounds to form the scrumpets. / Mel</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>contains_staple</t>
+          <t>meal_role</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
+          <t>snack</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="n"/>
       <c r="J46" s="3" t="n"/>
       <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>RCP2_130F971CF821</t>
+          <t>RCP2_5954131C04AC</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Ukrainian Bukovinian Nachynka (Cornbread Dressing)</t>
+          <t>Scrumpets</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>baked_good</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>onion 110.0 g（1 small onion, chopped fine）; butter 42.6 g（3 tablespoons butter）; cornmeal 157.0 g（1 cup cornmeal）; salt 6.1 g（1 teaspoon salt）; sugar 4.2 g（1 teaspoon sugar）; black_pepper 1.1 g（1/2 teaspoon pepper）; cinnamon 0.7 g（1/4 teaspoon cinnamon, if desired）; milk 854.0 g（3 1/2 cups scalded milk）; cream 119.0 g（1/2 cup light cream）; egg 125.0 g（2 -3 eggs, well beaten）</t>
+          <t>flour 500.0 g（4 cups all-purpose flour, sifted）; sugar 25.0 g（2 tablespoons white sugar）; baking_powder 18.3 g（4 teaspoons baking powder）; salt 6.1 g（1 teaspoon salt）; milk 244.0 g（1 cup milk）; egg 150.0 g（3 eggs）; butter 113.5 g（1/2 cup butter, melted）; butter 4.7 g（1 teaspoon butter, or as needed (optional)）</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Cook the onion in the butter until it is tender but not brown. / Add the corn meal along with the salt, sugar, pepper, and cinnamon, and mix them to coat the cereal thoroughly with the butter. / Pour in the scalded milk gradually and stir briskly until the mixture is smooth and free of lumps. / Cook until it thickens. / Remove it from the range and blend in the cream. / Beat the eggs well and fold</t>
+          <t>Place flour, sugar, baking powder, and salt in a bowl and mix well. / Beat milk, eggs, and melted butter together in another bowl; stir into the flour mixture with a few strokes. Handle dough as little as possible. / Scrape the dough out onto a generously floured surface. Dip your fingers in flour and pat dough into a circle about 1/2-inch thick. Cut into 4-inch rounds to form the scrumpets. / Mel</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>meal_role</t>
+          <t>contains_staple</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>staple</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>soup / staple / one_bowl / breakfast / snack / dessert / sauce / drink</t>
-        </is>
-      </c>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="n"/>
       <c r="J47" s="3" t="n"/>
       <c r="K47" s="3" t="n"/>
-      <c r="L47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -2768,91 +2625,85 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>RCP2_130F971CF821</t>
+          <t>RCP2_5D84F859E558</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Ukrainian Bukovinian Nachynka (Cornbread Dressing)</t>
+          <t>English Popovers</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>baked_good</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>onion 110.0 g（1 small onion, chopped fine）; butter 42.6 g（3 tablespoons butter）; cornmeal 157.0 g（1 cup cornmeal）; salt 6.1 g（1 teaspoon salt）; sugar 4.2 g（1 teaspoon sugar）; black_pepper 1.1 g（1/2 teaspoon pepper）; cinnamon 0.7 g（1/4 teaspoon cinnamon, if desired）; milk 854.0 g（3 1/2 cups scalded milk）; cream 119.0 g（1/2 cup light cream）; egg 125.0 g（2 -3 eggs, well beaten）</t>
+          <t>egg 100.0 g（2 eggs）; milk 244.0 g（1 c. milk）; flour 125.0 g（1 c. flour, sifted）</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Cook the onion in the butter until it is tender but not brown. / Add the corn meal along with the salt, sugar, pepper, and cinnamon, and mix them to coat the cereal thoroughly with the butter. / Pour in the scalded milk gradually and stir briskly until the mixture is smooth and free of lumps. / Cook until it thickens. / Remove it from the range and blend in the cream. / Beat the eggs well and fold</t>
+          <t>Put all ingredients in a blender. / Blend until smooth. / Fill 8 well-greased muffin tins or custard cups. / Bake at 400° for 10 minutes, then lower oven temperature to 350° for 20 minutes longer. / Serve warm with butter and jam.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>contains_staple</t>
+          <t>meal_role</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
+          <t>breakfast</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="n"/>
       <c r="J48" s="3" t="n"/>
       <c r="K48" s="3" t="n"/>
-      <c r="L48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>RCP2_1722D847EECE</t>
+          <t>RCP2_5D84F859E558</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Southern Spoon Bread</t>
+          <t>English Popovers</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>baked_good</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>milk 488.0 g（2 c. milk）; cornmeal 157.0 g（1 c. corn meal）; butter 56.8 g（4 Tbsp. butter）; egg 200.0 g（4 eggs, separated）; salt 18.2 g（1 Tbsp. salt）</t>
+          <t>egg 100.0 g（2 eggs）; milk 244.0 g（1 c. milk）; flour 125.0 g（1 c. flour, sifted）</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Pour milk into top of double boiler and cook until it almost comes to a boil. / Slowly add corn meal, stirring constantly. / Cook until mixture is thick and smooth, approximately 1 minute. / Add butter and salt and cool slightly. / Beat yolks and add to corn meal mixture. / Beat egg whites until stiff and fold into corn meal. Pour into buttered casserole dish and bake in preheated 375° oven for 35</t>
+          <t>Put all ingredients in a blender. / Blend until smooth. / Fill 8 well-greased muffin tins or custard cups. / Bake at 400° for 10 minutes, then lower oven temperature to 350° for 20 minutes longer. / Serve warm with butter and jam.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>meal_role</t>
+          <t>contains_staple</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>staple</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>soup / staple / one_bowl / breakfast / snack / dessert / sauce / drink</t>
-        </is>
-      </c>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="n"/>
       <c r="J49" s="3" t="n"/>
       <c r="K49" s="3" t="n"/>
-      <c r="L49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -2860,12 +2711,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>RCP2_1722D847EECE</t>
+          <t>RCP2_6336ACA2F9AE</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Southern Spoon Bread</t>
+          <t>Japanese Tamago Egg</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2875,76 +2726,70 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>milk 488.0 g（2 c. milk）; cornmeal 157.0 g（1 c. corn meal）; butter 56.8 g（4 Tbsp. butter）; egg 200.0 g（4 eggs, separated）; salt 18.2 g（1 Tbsp. salt）</t>
+          <t>egg 200.0 g（4 eggs）; dashi 59.1 g（1/4 cup prepared dashi stock）; sugar 12.5 g（1 tablespoon white sugar）; mirin 5.6 g（1 teaspoon mirin (Japanese sweet wine)）; soy_sauce 2.7 g（1/2 teaspoon soy sauce）; vegetable_oil 2.3 g（1/2 teaspoon vegetable oil, or more as needed）</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Pour milk into top of double boiler and cook until it almost comes to a boil. / Slowly add corn meal, stirring constantly. / Cook until mixture is thick and smooth, approximately 1 minute. / Add butter and salt and cool slightly. / Beat yolks and add to corn meal mixture. / Beat egg whites until stiff and fold into corn meal. Pour into buttered casserole dish and bake in preheated 375° oven for 35</t>
+          <t xml:space="preserve">Beat eggs thoroughly in a bowl; whisk in dashi stock, sugar, mirin, and soy sauce until sugar has dissolved. / Place a nonstick skillet or omelet pan over medium heat. Oil the pan with vegetable oil. Pour a thin layer of egg mixture into the hot pan and swirl to coat pan. / When egg layer is firm on the bottom but still slightly liquid on top, lift up about 1 inch of the edge of the omelet with a </t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>contains_staple</t>
+          <t>meal_role</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
+          <t>protein_main</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="n"/>
       <c r="J50" s="3" t="n"/>
       <c r="K50" s="3" t="n"/>
-      <c r="L50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>RCP2_310A97E81CC3</t>
+          <t>RCP2_6336ACA2F9AE</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Taco Baked Potatoes</t>
+          <t>Japanese Tamago Egg</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>side</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>potato 852.0 g（4 medium baking potatoes）; yogurt 245.0 g（1 c. plain yogurt）; black_pepper 0.3 g（1/8 tsp. pepper）; cheddar 84.8 g（3/4 c. shredded Cheddar）; green_chili 75.0 g（1/2 c. chopped, well drained green chilies）; pimento 48.0 g（1/4 c. chopped pimentos, well drained）; cilantro 1.0 g（1 Tbsp. chopped cilantro）; lime_juice 15.1 g（1 Tbsp. lime juice）; avocado 150.0 g（1 ripe avocado）</t>
+          <t>egg 200.0 g（4 eggs）; dashi 59.1 g（1/4 cup prepared dashi stock）; sugar 12.5 g（1 tablespoon white sugar）; mirin 5.6 g（1 teaspoon mirin (Japanese sweet wine)）; soy_sauce 2.7 g（1/2 teaspoon soy sauce）; vegetable_oil 2.3 g（1/2 teaspoon vegetable oil, or more as needed）</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Wash potatoes well. / Bake potatoes at 400° for 1 hour or until soft. / Cut potatoes in half lengthwise, carefully scoop out potato pulp into bowl (leave 1/2-inch pulp to keep potato skin intact). Set skins aside. / Add yogurt and pepper to pulp; mash until fluffy. Stir in 1/2 cup cheese, chilies, pimento and cilantro into mixture. Stuff skins with mixture. / Place stuffed potatoes on ungreased ba</t>
+          <t xml:space="preserve">Beat eggs thoroughly in a bowl; whisk in dashi stock, sugar, mirin, and soy sauce until sugar has dissolved. / Place a nonstick skillet or omelet pan over medium heat. Oil the pan with vegetable oil. Pour a thin layer of egg mixture into the hot pan and swirl to coat pan. / When egg layer is firm on the bottom but still slightly liquid on top, lift up about 1 inch of the edge of the omelet with a </t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>meal_role</t>
+          <t>contains_staple</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>staple</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>soup / staple / one_bowl / breakfast / snack / dessert / sauce / drink</t>
-        </is>
-      </c>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="n"/>
       <c r="J51" s="3" t="n"/>
       <c r="K51" s="3" t="n"/>
-      <c r="L51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -2952,43 +2797,42 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>RCP2_310A97E81CC3</t>
+          <t>RCP2_6AD2450270A2</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Taco Baked Potatoes</t>
+          <t>Russian Wafers</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>baked_good</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>potato 852.0 g（4 medium baking potatoes）; yogurt 245.0 g（1 c. plain yogurt）; black_pepper 0.3 g（1/8 tsp. pepper）; cheddar 84.8 g（3/4 c. shredded Cheddar）; green_chili 75.0 g（1/2 c. chopped, well drained green chilies）; pimento 48.0 g（1/4 c. chopped pimentos, well drained）; cilantro 1.0 g（1 Tbsp. chopped cilantro）; lime_juice 15.1 g（1 Tbsp. lime juice）; avocado 150.0 g（1 ripe avocado）</t>
+          <t>powdered_sugar 60.0 g（1/2 c. sifted powdered sugar）; butter 113.5 g（1/2 c. butter）; shortening 153.8 g（3/4 c. Crisco）; salt 6.1 g（1 tsp. salt）; vanilla 26.0 g（2 Tbsp. vanilla）; flour 250.0 g（2 c. flour）; pecan 178.5 g（1 1/2 c. chopped pecans）</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Wash potatoes well. / Bake potatoes at 400° for 1 hour or until soft. / Cut potatoes in half lengthwise, carefully scoop out potato pulp into bowl (leave 1/2-inch pulp to keep potato skin intact). Set skins aside. / Add yogurt and pepper to pulp; mash until fluffy. Stir in 1/2 cup cheese, chilies, pimento and cilantro into mixture. Stuff skins with mixture. / Place stuffed potatoes on ungreased ba</t>
+          <t>Mix first 5 ingredients together and add flour and 1 1/2 cups finely chopped pecans. / Drop by teaspoon on a cookie sheet and bake at 325° for 25 minutes. / Roll in powdered sugar while still warm; these are very rich and have to be handled carefully.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>contains_staple</t>
+          <t>protein_sources</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="n"/>
       <c r="J52" s="3" t="n"/>
       <c r="K52" s="3" t="n"/>
-      <c r="L52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -2996,27 +2840,27 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>RCP2_3CC1354BC571</t>
+          <t>RCP2_75BFE1C39E34</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Brazilian Arroz De Festa (Confetti Rice)</t>
+          <t>Taco Casserole</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>main</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>vegetable_oil 34.1 g（2 1/2 tablespoons vegetable oil）; onion 40.0 g（1/4 cup minced onion）; garlic 9.0 g（3 large cloves garlic, minced）; rice 370.0 g（2 cups basmati rice, rinsed and drained）; salt 6.1 g（1 teaspoon salt）; water 948.0 g（4 cups hot water）; carrot 122.0 g（2 carrots, peeled and chopped）; bell_pepper 120.0 g（1 green bell pepper, chopped）; bell_pepper 120.0 g（1 red bell pepper, chopped）; corn 432.3 g（1 (15.25 ounce) can whole kernel corn, drained）; butter 28.4 g（2 tablespoons butter, divided (optional)）; raisin 72.5 g（1/2 cup raisins）; cranberry 50.0 g（1/2 cup dried cranberries）; raisin 36.2 g（1/4 cup golden raisins）</t>
+          <t>mashed_potatoes 420.0 g（2 c. instant mashed potatoes）; sour_cream 345.0 g（1 1/2 c. sour cream）; water 59.2 g（1/4 c. water）</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Heat oil in a saucepan over medium heat. Cook and stir onion for 1 minute. Add garlic; cook until golden brown, about 1 minute. Add rice and salt; cook rice until it starts to brown, 3 to 5 minutes. Pour in hot water. Reduce heat to low, cover, and simmer until water has been absorbed, 20 to 25 minutes. / Place carrots in a saucepan with enough water to cover. Cook over medium-high heat for 5 minu</t>
+          <t>For crust, mix potatoes, sour cream and water and pat into bottom of 9 x 12-inch pan. / Bake at 350° for 20 minutes or until edges start browning.</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -3026,17 +2870,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>staple</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>soup / staple / one_bowl / breakfast / snack / dessert / sauce / drink</t>
-        </is>
-      </c>
+          <t>sauce</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="n"/>
       <c r="J53" s="3" t="n"/>
       <c r="K53" s="3" t="n"/>
-      <c r="L53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -3044,27 +2883,27 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>RCP2_3CC1354BC571</t>
+          <t>RCP2_75BFE1C39E34</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Brazilian Arroz De Festa (Confetti Rice)</t>
+          <t>Taco Casserole</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>main</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>vegetable_oil 34.1 g（2 1/2 tablespoons vegetable oil）; onion 40.0 g（1/4 cup minced onion）; garlic 9.0 g（3 large cloves garlic, minced）; rice 370.0 g（2 cups basmati rice, rinsed and drained）; salt 6.1 g（1 teaspoon salt）; water 948.0 g（4 cups hot water）; carrot 122.0 g（2 carrots, peeled and chopped）; bell_pepper 120.0 g（1 green bell pepper, chopped）; bell_pepper 120.0 g（1 red bell pepper, chopped）; corn 432.3 g（1 (15.25 ounce) can whole kernel corn, drained）; butter 28.4 g（2 tablespoons butter, divided (optional)）; raisin 72.5 g（1/2 cup raisins）; cranberry 50.0 g（1/2 cup dried cranberries）; raisin 36.2 g（1/4 cup golden raisins）</t>
+          <t>mashed_potatoes 420.0 g（2 c. instant mashed potatoes）; sour_cream 345.0 g（1 1/2 c. sour cream）; water 59.2 g（1/4 c. water）</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Heat oil in a saucepan over medium heat. Cook and stir onion for 1 minute. Add garlic; cook until golden brown, about 1 minute. Add rice and salt; cook rice until it starts to brown, 3 to 5 minutes. Pour in hot water. Reduce heat to low, cover, and simmer until water has been absorbed, 20 to 25 minutes. / Place carrots in a saucepan with enough water to cover. Cook over medium-high heat for 5 minu</t>
+          <t>For crust, mix potatoes, sour cream and water and pat into bottom of 9 x 12-inch pan. / Bake at 350° for 20 minutes or until edges start browning.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -3074,13 +2913,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="n"/>
       <c r="J54" s="3" t="n"/>
       <c r="K54" s="3" t="n"/>
-      <c r="L54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -3088,27 +2926,27 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>RCP2_409262770DBA</t>
+          <t>RCP2_806075FC7BF8</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Popovers(Portuguese)</t>
+          <t>French Onion Soup</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>baked_good</t>
+          <t>soup</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>flour 125.0 g（1 c. sifted flour）; milk 244.0 g（1 c. milk）; salt 3.0 g（1/2 tsp. salt）; egg 100.0 g（2 eggs）</t>
+          <t>onion 453.6 g（1 lb. yellow onions, sliced）; butter 56.8 g（1/4 c. butter）; flour 15.6 g（2 Tbsp. flour）; water 948.0 g（4 c. water）; bouillon 20.0 g（5 beef bouillon cubes）; salt 3.0 g（1/2 tsp. salt）; bread 116.0 g（4 slices French bread, toasted）; parmesan 50.0 g（1/2 c. Parmesan cheese）</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Beat together ingredients with rotary beater just until smooth. / Pour into well-greased deep muffin cup (3/4 full) or oven glass cups (1/2 full). Bake at 425° for 35 to 45 minutes.</t>
+          <t>Saute onions in butter in heavy saucepan. / Stir in flour. Cook until flour is lightly browned. / Add water, bouillon and salt. / Bring to a boil, stirring to dissolve bouillon. / Simmer, covered, for 15 minutes. / Ladle into ovenproof bowls. / Top with French bread. / Sprinkle with cheese. / Broil until cheese is light brown. / Yield: 4 servings.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -3118,17 +2956,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>staple</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>protein_main / staple / one_bowl / breakfast / snack / dessert</t>
-        </is>
-      </c>
+          <t>soup</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="n"/>
       <c r="J55" s="3" t="n"/>
       <c r="K55" s="3" t="n"/>
-      <c r="L55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -3136,27 +2969,27 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>RCP2_409262770DBA</t>
+          <t>RCP2_806075FC7BF8</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Popovers(Portuguese)</t>
+          <t>French Onion Soup</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>baked_good</t>
+          <t>soup</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>flour 125.0 g（1 c. sifted flour）; milk 244.0 g（1 c. milk）; salt 3.0 g（1/2 tsp. salt）; egg 100.0 g（2 eggs）</t>
+          <t>onion 453.6 g（1 lb. yellow onions, sliced）; butter 56.8 g（1/4 c. butter）; flour 15.6 g（2 Tbsp. flour）; water 948.0 g（4 c. water）; bouillon 20.0 g（5 beef bouillon cubes）; salt 3.0 g（1/2 tsp. salt）; bread 116.0 g（4 slices French bread, toasted）; parmesan 50.0 g（1/2 c. Parmesan cheese）</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Beat together ingredients with rotary beater just until smooth. / Pour into well-greased deep muffin cup (3/4 full) or oven glass cups (1/2 full). Bake at 425° for 35 to 45 minutes.</t>
+          <t>Saute onions in butter in heavy saucepan. / Stir in flour. Cook until flour is lightly browned. / Add water, bouillon and salt. / Bring to a boil, stirring to dissolve bouillon. / Simmer, covered, for 15 minutes. / Ladle into ovenproof bowls. / Top with French bread. / Sprinkle with cheese. / Broil until cheese is light brown. / Yield: 4 servings.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -3166,13 +2999,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="n"/>
       <c r="J56" s="3" t="n"/>
       <c r="K56" s="3" t="n"/>
-      <c r="L56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -3180,27 +3012,27 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>RCP2_50567B7B0B2C</t>
+          <t>RCP2_81C30294D91B</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Kumpir</t>
+          <t>Turkish Pogaca</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>baked_good</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>potato 426.0 g（2 large Potatoes）; butter 28.4 g（2 tbs Butter）; cheese 150.0 g（150g Cheese）; onion 110.0 g（1 large Onion）; bell_pepper 120.0 g（1 large Red Pepper）; cayenne 0.2 g（Pinch Red Chilli Flakes）</t>
+          <t>flour 600.0 g（600 g flour）; milk 309.4 g（300 ml nonfat milk）; sugar 10.0 g（10 g sugar）; yeast 7.1 g（1/4 ounce yeast）; vegetable_oil 161.3 g（175 ml vegetable oil）; egg 50.0 g（1 egg）; egg_yolk 17.0 g（1 egg yolk）; salt 6.1 g（1 teaspoon salt）; poppy_seed 9.0 g（1 tablespoon poppy seed）; feta 150.0 g（1 cup feta cheese）; parsley 60.0 g（1 cup parsley）</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>If you order kumpir in Turkey, the standard filling is first, lots of butter mashed into the potato, followed by cheese. There’s then a row of other toppings that you can just point at to your heart’s content – sweetcorn, olives, salami, coleslaw, Russian salad, allsorts – and you walk away with an over-stuffed potato because you got ever-excited by the choices on offer. / Grate (roughly – you can</t>
+          <t>Mix everything together except the egg yolk. / Wait for 1 hour for batter to double. / Make small rounds as big as half of your palm. / Press it with your fingers to make it as big as your palm. / Mix feta cheese and parsley. / Put the mixture into these small rounds and close it and round it again. / Place it on the oiled oven sheet. / Brush all the batch with the egg yolk. / Place it in the preh</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -3210,17 +3042,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>staple</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>soup / staple / one_bowl / breakfast / snack / dessert / sauce / drink</t>
-        </is>
-      </c>
+          <t>snack</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="n"/>
       <c r="J57" s="3" t="n"/>
       <c r="K57" s="3" t="n"/>
-      <c r="L57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -3228,27 +3055,27 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>RCP2_50567B7B0B2C</t>
+          <t>RCP2_81C30294D91B</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Kumpir</t>
+          <t>Turkish Pogaca</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>baked_good</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>potato 426.0 g（2 large Potatoes）; butter 28.4 g（2 tbs Butter）; cheese 150.0 g（150g Cheese）; onion 110.0 g（1 large Onion）; bell_pepper 120.0 g（1 large Red Pepper）; cayenne 0.2 g（Pinch Red Chilli Flakes）</t>
+          <t>flour 600.0 g（600 g flour）; milk 309.4 g（300 ml nonfat milk）; sugar 10.0 g（10 g sugar）; yeast 7.1 g（1/4 ounce yeast）; vegetable_oil 161.3 g（175 ml vegetable oil）; egg 50.0 g（1 egg）; egg_yolk 17.0 g（1 egg yolk）; salt 6.1 g（1 teaspoon salt）; poppy_seed 9.0 g（1 tablespoon poppy seed）; feta 150.0 g（1 cup feta cheese）; parsley 60.0 g（1 cup parsley）</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>If you order kumpir in Turkey, the standard filling is first, lots of butter mashed into the potato, followed by cheese. There’s then a row of other toppings that you can just point at to your heart’s content – sweetcorn, olives, salami, coleslaw, Russian salad, allsorts – and you walk away with an over-stuffed potato because you got ever-excited by the choices on offer. / Grate (roughly – you can</t>
+          <t>Mix everything together except the egg yolk. / Wait for 1 hour for batter to double. / Make small rounds as big as half of your palm. / Press it with your fingers to make it as big as your palm. / Mix feta cheese and parsley. / Put the mixture into these small rounds and close it and round it again. / Place it on the oiled oven sheet. / Brush all the batch with the egg yolk. / Place it in the preh</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -3258,13 +3085,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="n"/>
       <c r="J58" s="3" t="n"/>
       <c r="K58" s="3" t="n"/>
-      <c r="L58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -3272,12 +3098,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>RCP2_12D50BBDB52E</t>
+          <t>RCP2_8F83C05E5E00</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Eggplant A La Parmesan</t>
+          <t>Siopao (Filipino Steamed Buns)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3287,12 +3113,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>eggplant 300.0 g（1 medium eggplant, peeled and sliced in 1/2-inch slices）; tomato 369.0 g（3 large tomatoes, peeled and sliced）; onion 110.0 g（1 large onion, sliced and separated into rings）; margarine 170.2 g（3/4 c. margarine, melted）; basil 0.2 g（1/2 tsp. basil）; garlic_salt 4.5 g（3/4 tsp. garlic salt）; mozzarella 226.8 g（1/2 lb. Mozzarella cheese, shredded）; bread 116.0 g（4 slices bread (made into crumbs)）; parmesan 31.2 g（4 to 6 Tbsp. Parmesan cheese）</t>
+          <t>flour 416.7 g（3 1/3 cups all-purpose flour）; sugar 100.0 g（1/2 cup white sugar）; salt 3.0 g（1/2 teaspoon salt）; yeast 7.0 g（1 (.25 ounce) package active dry yeast）; water 237.0 g（1 cup lukewarm water）; vegetable_oil 54.5 g（1/4 cup vegetable oil）; vegetable_oil 4.5 g（1 teaspoon vegetable oil, or as needed）</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preheat oven to 450°. / Arrange eggplant in the bottom of a 9 x 13-inch aluminum pan or Pyrex dish. / Top with onion, then tomatoes. Drizzle 1/2 cup margarine over entire casserole. / Sprinkle with basil and garlic salt. / Cover and bake for 20 to 30 minutes. Remove from oven and top with Mozzarella cheese. / Toss crumbs with 1/4 cup melted margarine and spread over casserole. / Top with Parmesan </t>
+          <t xml:space="preserve">Mix flour, sugar, salt, and yeast together in a large bowl. Add water and 1/4 cup oil; mix into a dough. Knead until smooth and elastic, at least 10 minutes. Dust with extra flour if necessary. / Warm up the oven for 1 minute. Turn oven off. / Oil a large bowl; place dough inside and cover with cheesecloth. Place in the warmed oven until size has doubled, about 1 hour. / Punch down dough. Keep in </t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -3302,17 +3128,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>vegetable</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>vegetable / staple</t>
-        </is>
-      </c>
+          <t>sauce</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="n"/>
       <c r="J59" s="3" t="n"/>
       <c r="K59" s="3" t="n"/>
-      <c r="L59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -3320,12 +3141,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>RCP2_12D50BBDB52E</t>
+          <t>RCP2_8F83C05E5E00</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Eggplant A La Parmesan</t>
+          <t>Siopao (Filipino Steamed Buns)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3335,12 +3156,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>eggplant 300.0 g（1 medium eggplant, peeled and sliced in 1/2-inch slices）; tomato 369.0 g（3 large tomatoes, peeled and sliced）; onion 110.0 g（1 large onion, sliced and separated into rings）; margarine 170.2 g（3/4 c. margarine, melted）; basil 0.2 g（1/2 tsp. basil）; garlic_salt 4.5 g（3/4 tsp. garlic salt）; mozzarella 226.8 g（1/2 lb. Mozzarella cheese, shredded）; bread 116.0 g（4 slices bread (made into crumbs)）; parmesan 31.2 g（4 to 6 Tbsp. Parmesan cheese）</t>
+          <t>flour 416.7 g（3 1/3 cups all-purpose flour）; sugar 100.0 g（1/2 cup white sugar）; salt 3.0 g（1/2 teaspoon salt）; yeast 7.0 g（1 (.25 ounce) package active dry yeast）; water 237.0 g（1 cup lukewarm water）; vegetable_oil 54.5 g（1/4 cup vegetable oil）; vegetable_oil 4.5 g（1 teaspoon vegetable oil, or as needed）</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preheat oven to 450°. / Arrange eggplant in the bottom of a 9 x 13-inch aluminum pan or Pyrex dish. / Top with onion, then tomatoes. Drizzle 1/2 cup margarine over entire casserole. / Sprinkle with basil and garlic salt. / Cover and bake for 20 to 30 minutes. Remove from oven and top with Mozzarella cheese. / Toss crumbs with 1/4 cup melted margarine and spread over casserole. / Top with Parmesan </t>
+          <t xml:space="preserve">Mix flour, sugar, salt, and yeast together in a large bowl. Add water and 1/4 cup oil; mix into a dough. Knead until smooth and elastic, at least 10 minutes. Dust with extra flour if necessary. / Warm up the oven for 1 minute. Turn oven off. / Oil a large bowl; place dough inside and cover with cheesecloth. Place in the warmed oven until size has doubled, about 1 hour. / Punch down dough. Keep in </t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -3353,10 +3174,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
+      <c r="I60" s="3" t="n"/>
       <c r="J60" s="3" t="n"/>
       <c r="K60" s="3" t="n"/>
-      <c r="L60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -3364,28 +3184,27 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>RCP2_441BD2095B93</t>
+          <t>RCP2_956FD7177508</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Vietnamese Pâté Chaud</t>
+          <t>Ramen Hot And Sour Soup</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>snack_appetizer</t>
+          <t>soup</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>pork 300.0 g（300 grams ground pork）; pate 75.0 g（75 grams pate）; onion 110.0 g（1 yellow onion, finely diced）; salt 3.0 g（1/2 teaspoon salt (or more to taste)）; black_pepper 1.1 g（1/2 teaspoon ground black pepper）; sugar 1.0 g（1/4 teaspoon sugar）; potato_starch 8.0 g（2 teaspoons potato starch）; puff_pastry 490.0 g（2 sheets of puff pastry）; egg 50.0 g（1 egg beaten）</t>
+          <t>ramen 85.0 g（1 (3 ounce) package ramen noodles）; water 474.0 g（2 cups water）; mushroom 8.8 g（1/8 cup mushroom, thinly sliced）; rice_vinegar 16.1 g（1 tablespoon rice vinegar）; chili_sauce 0.6 g（1/8 teaspoon chili sauce）; egg 50.0 g（1 egg, beaten）; meat 17.5 g（1/8 cup meat, cooked, sliced thinly. (optional)）; green_onion 15.0 g（1 green onion, light and dark green parts, sliced thin）</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Filling: Combine the pork, pate, onion, potato starch and season with salt, sugar and pepper. Mix thoroughly until all of the ingredients are uniformly amalgamated. To ensure that the mixture is properly seasoned, add the salt gradually and taste after each addition by cooking a spoonful in the microwave (but without the spoon). / Preheat oven to 175°C.
-Work with one pastry sheet at time, leaving</t>
+          <t>Put 2 cups of warm water in saucepan. Add Ramen Noodles and Mushrooms. Bring to boil. / Add Rice Vinegar and Chili Sauce, cook till noodles are tender, about 5-7 minutes. Turn heat down to medium. / Add the sliced meat if desired. You can use beef, pork, or uncooked small shrimp. / Very slowly drizzle in the beaten egg so that it kinda forms a solid mass on top of the soup. Once the egg is kinda s</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -3395,13 +3214,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>pork</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr"/>
+          <t>egg</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="n"/>
       <c r="J61" s="3" t="n"/>
       <c r="K61" s="3" t="n"/>
-      <c r="L61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -3409,12 +3227,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>RCP2_03DEE14CDC60</t>
+          <t>RCP2_A31F833871D7</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Hush Puppies</t>
+          <t>Bread Dumplings</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3424,12 +3242,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>cornmeal 157.0 g（1 c. cornmeal）; flour 125.0 g（1 c. flour）; baking_powder 9.2 g（2 tsp. baking powder）; salt 6.1 g（1 tsp. salt）; garlic_salt 3.0 g（1/2 tsp. garlic salt）; onion 20.0 g（2 Tbsp. diced onion）; egg 50.0 g（1 egg）; milk 183.0 g（3/4 c. milk）</t>
+          <t>bread 87.0 g（3 slices white bread）; butter 28.4 g（2 Tbsp. butter）; flour 187.5 g（1 1/2 c. sifted flour）; salt 18.2 g（1 Tbsp. salt）; egg 50.0 g（1 beaten egg）; milk 183.0 g（3/4 c. milk）</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Add and blend all ingredients. / Drop by teaspoonfuls into hot oil and fry to a golden brown. / Drain on paper towels and serve hot. / Serves 4 to 6.</t>
+          <t>Dice and fry bread in butter until crisp. / Remove and place on paper towel. / In large bowl, mix flour and salt. / Mix egg and milk and stir into flour mixture. / Form into dumplings around bread cubes, using 3 to 4 cubes per dumpling. / Drop into boiling water, taking care that dumplings do not stick. / Cover and boil gently 15 to 20 minutes or until done. / Makes 4 servings.</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3442,10 +3260,9 @@
           <t>staple</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
+      <c r="I62" s="3" t="n"/>
       <c r="J62" s="3" t="n"/>
       <c r="K62" s="3" t="n"/>
-      <c r="L62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -3453,12 +3270,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>RCP2_03DEE14CDC60</t>
+          <t>RCP2_A31F833871D7</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Hush Puppies</t>
+          <t>Bread Dumplings</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3468,12 +3285,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>cornmeal 157.0 g（1 c. cornmeal）; flour 125.0 g（1 c. flour）; baking_powder 9.2 g（2 tsp. baking powder）; salt 6.1 g（1 tsp. salt）; garlic_salt 3.0 g（1/2 tsp. garlic salt）; onion 20.0 g（2 Tbsp. diced onion）; egg 50.0 g（1 egg）; milk 183.0 g（3/4 c. milk）</t>
+          <t>bread 87.0 g（3 slices white bread）; butter 28.4 g（2 Tbsp. butter）; flour 187.5 g（1 1/2 c. sifted flour）; salt 18.2 g（1 Tbsp. salt）; egg 50.0 g（1 beaten egg）; milk 183.0 g（3/4 c. milk）</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Add and blend all ingredients. / Drop by teaspoonfuls into hot oil and fry to a golden brown. / Drain on paper towels and serve hot. / Serves 4 to 6.</t>
+          <t>Dice and fry bread in butter until crisp. / Remove and place on paper towel. / In large bowl, mix flour and salt. / Mix egg and milk and stir into flour mixture. / Form into dumplings around bread cubes, using 3 to 4 cubes per dumpling. / Drop into boiling water, taking care that dumplings do not stick. / Cover and boil gently 15 to 20 minutes or until done. / Makes 4 servings.</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -3486,23 +3303,22 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
+      <c r="I63" s="3" t="n"/>
       <c r="J63" s="3" t="n"/>
       <c r="K63" s="3" t="n"/>
-      <c r="L63" s="3" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>RCP2_1729D7258E04</t>
+          <t>RCP2_A31F833871D7</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Egg Filling For Sushi</t>
+          <t>Bread Dumplings</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3512,28 +3328,27 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>egg 100.0 g（2 eggs）; flour 15.6 g（2 tablespoons flour）; sugar 25.0 g（2 tablespoons sugar）; salt 6.1 g（1 teaspoon salt）</t>
+          <t>bread 87.0 g（3 slices white bread）; butter 28.4 g（2 Tbsp. butter）; flour 187.5 g（1 1/2 c. sifted flour）; salt 18.2 g（1 Tbsp. salt）; egg 50.0 g（1 beaten egg）; milk 183.0 g（3/4 c. milk）</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>In a bowl beat all ingredients together. / Heat a non stick or lightly oiled pan on a medium heat. I normally use a small frying pan to give me a 1/4 inch thick omelette. / Cook until golden on both sides. / Allow to cool and slice into 1/2 inch thick slices.</t>
+          <t>Dice and fry bread in butter until crisp. / Remove and place on paper towel. / In large bowl, mix flour and salt. / Mix egg and milk and stir into flour mixture. / Form into dumplings around bread cubes, using 3 to 4 cubes per dumpling. / Drop into boiling water, taking care that dumplings do not stick. / Cover and boil gently 15 to 20 minutes or until done. / Makes 4 servings.</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>meal_role</t>
+          <t>protein_sources</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>sauce</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="n"/>
       <c r="J64" s="3" t="n"/>
       <c r="K64" s="3" t="n"/>
-      <c r="L64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -3541,100 +3356,98 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>RCP2_1729D7258E04</t>
+          <t>RCP2_A887D44E2FC0</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Egg Filling For Sushi</t>
+          <t>Sauerkraut pierogii</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>main</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>egg 100.0 g（2 eggs）; flour 15.6 g（2 tablespoons flour）; sugar 25.0 g（2 tablespoons sugar）; salt 6.1 g（1 teaspoon salt）</t>
+          <t>sunflower_oil 13.6 g（1 tablespoon Sunflower Oil）; shallot 80.0 g（2 chopped Shallots）; sauerkraut 150.0 g（150g Sauerkraut）; cabbage 150.0 g（150g Hispi (sweetheart) Cabbage）; egg 50.0 g（1 beaten Egg）; vegetable_oil 6.8 g（1/2 tbs Vegetable Oil）; flour 350.0 g（350g Plain Flour）; vegetable_oil 230.4 g（For frying Vegetable Oil）; shallot 80.0 g（2 sliced Shallots）; flour 15.6 g（Dusting Plain Flour）; butter 45.0 g（45g Butter）; sour_cream 58.3 g（60 ml Sour Cream）</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>In a bowl beat all ingredients together. / Heat a non stick or lightly oiled pan on a medium heat. I normally use a small frying pan to give me a 1/4 inch thick omelette. / Cook until golden on both sides. / Allow to cool and slice into 1/2 inch thick slices.</t>
+          <t>First, make the crispy shallots. Heat the oil in a saucepan to 180C (a cube of bread will turn golden in 15 secs). Toss the shallots in a little flour and deep-fry for 1 min or until light golden and crispy. Drain on kitchen paper. Can be made up to two days before and kept in an airtight container. / To make the filling, heat the oil in a medium non-stick frying pan and gently fry the shallots fo</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>contains_staple</t>
+          <t>meal_role</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr"/>
+          <t>snack</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="n"/>
       <c r="J65" s="3" t="n"/>
       <c r="K65" s="3" t="n"/>
-      <c r="L65" s="3" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>RCP2_1EF61A58359F</t>
+          <t>RCP2_A887D44E2FC0</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Apple Casserole</t>
+          <t>Sauerkraut pierogii</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>main</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>apple 880.0 g（8 c. sliced tart apples）; cranberry 200.0 g（2 c. raw cranberries, washed）; sugar 150.0 g（3/4 c. sugar）; margarine 113.5 g（1 stick margarine）; oats 81.0 g（1 c. uncooked oatmeal）; flour 41.7 g（1/3 c. flour）; brown_sugar 110.0 g（1/2 c. brown sugar）; mixed_nuts 60.0 g（1/2 c. chopped nuts）</t>
+          <t>sunflower_oil 13.6 g（1 tablespoon Sunflower Oil）; shallot 80.0 g（2 chopped Shallots）; sauerkraut 150.0 g（150g Sauerkraut）; cabbage 150.0 g（150g Hispi (sweetheart) Cabbage）; egg 50.0 g（1 beaten Egg）; vegetable_oil 6.8 g（1/2 tbs Vegetable Oil）; flour 350.0 g（350g Plain Flour）; vegetable_oil 230.4 g（For frying Vegetable Oil）; shallot 80.0 g（2 sliced Shallots）; flour 15.6 g（Dusting Plain Flour）; butter 45.0 g（45g Butter）; sour_cream 58.3 g（60 ml Sour Cream）</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Into greased casserole (I use margarine for greasing), add apples and cranberries. / Sprinkle with 3/4 cup sugar (this can be done the day before and refrigerated). / Mix melted margarine, oatmeal, flour, brown sugar and nuts. / Sprinkle over apples and cranberries. / Bake approximately 1 hour in 350° oven. / Serves 12 plus. / May be used as side dish or dessert.</t>
+          <t>First, make the crispy shallots. Heat the oil in a saucepan to 180C (a cube of bread will turn golden in 15 secs). Toss the shallots in a little flour and deep-fry for 1 min or until light golden and crispy. Drain on kitchen paper. Can be made up to two days before and kept in an airtight container. / To make the filling, heat the oil in a medium non-stick frying pan and gently fry the shallots fo</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>protein_sources</t>
+          <t>contains_staple</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="n"/>
       <c r="J66" s="3" t="n"/>
       <c r="K66" s="3" t="n"/>
-      <c r="L66" s="3" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>RCP2_23DCDA368745</t>
+          <t>RCP2_A96FC949077E</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Homemade Nama (Fresh) Udon Noodles</t>
+          <t>Moroccan Lentils And Couscous</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3644,12 +3457,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>bread_flour 190.5 g（1 1/2 cups bread flour）; flour 187.5 g（1 1/2 cups all-purpose flour）; salt 6.1 g（1 teaspoon salt）; water 237.0 g（1 cup water）</t>
+          <t>lentil 192.0 g（1 cup lentils, uncooked）; garlic 12.0 g（4 garlic cloves, crushed）; cumin 2.2 g（1 teaspoon cumin, ground）; salt 3.0 g（1/2 teaspoon salt）; black_pepper 0.3 g（1/8 teaspoon pepper）; cinnamon 0.2 g（1/16 teaspoon ground cinnamon）; bay_leaf 0.2 g（1 bay leaf）; water 711.0 g（3 cups water）; vegetable_oil 9.1 g（2 teaspoons vegetable oil）; onion 320.0 g（2 cups onions, cut in thin slices）; couscous 86.5 g（1/2 cup couscous, uncooked）</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Combine bread flour, all-purpose flour, and salt together in a large bowl. Mix in water slowly until dough comes together into a rough ball. / Turn dough out onto a work surface and knead until smooth and elastic, about 15 minutes. Wrap dough in plastic wrap and refrigerate, at least 3 hours or overnight. / Remove dough from the refrigerator and cut in half. Dust the dough, rolling pin, and your w</t>
+          <t>Place the lentils in a medium saucepan. / Add garlic, spices, and 3 cups of water. Bring to a boil over medium heat, stirring occasionally. / Reduce heat to low, cover, and simmer 40 minutes, stirring once halfway through cooking time. / While lentils are cooking, bring 1 cup of water to a boil in a small saucepan. / Remove from heat, stir in couscous, cover, and set aside for 15 minutes. / Heat o</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -3659,26 +3472,25 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>staple</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr"/>
+          <t>one_bowl</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="n"/>
       <c r="J67" s="3" t="n"/>
       <c r="K67" s="3" t="n"/>
-      <c r="L67" s="3" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>RCP2_23DCDA368745</t>
+          <t>RCP2_A96FC949077E</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Homemade Nama (Fresh) Udon Noodles</t>
+          <t>Moroccan Lentils And Couscous</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3688,12 +3500,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>bread_flour 190.5 g（1 1/2 cups bread flour）; flour 187.5 g（1 1/2 cups all-purpose flour）; salt 6.1 g（1 teaspoon salt）; water 237.0 g（1 cup water）</t>
+          <t>lentil 192.0 g（1 cup lentils, uncooked）; garlic 12.0 g（4 garlic cloves, crushed）; cumin 2.2 g（1 teaspoon cumin, ground）; salt 3.0 g（1/2 teaspoon salt）; black_pepper 0.3 g（1/8 teaspoon pepper）; cinnamon 0.2 g（1/16 teaspoon ground cinnamon）; bay_leaf 0.2 g（1 bay leaf）; water 711.0 g（3 cups water）; vegetable_oil 9.1 g（2 teaspoons vegetable oil）; onion 320.0 g（2 cups onions, cut in thin slices）; couscous 86.5 g（1/2 cup couscous, uncooked）</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Combine bread flour, all-purpose flour, and salt together in a large bowl. Mix in water slowly until dough comes together into a rough ball. / Turn dough out onto a work surface and knead until smooth and elastic, about 15 minutes. Wrap dough in plastic wrap and refrigerate, at least 3 hours or overnight. / Remove dough from the refrigerator and cut in half. Dust the dough, rolling pin, and your w</t>
+          <t>Place the lentils in a medium saucepan. / Add garlic, spices, and 3 cups of water. Bring to a boil over medium heat, stirring occasionally. / Reduce heat to low, cover, and simmer 40 minutes, stirring once halfway through cooking time. / While lentils are cooking, bring 1 cup of water to a boil in a small saucepan. / Remove from heat, stir in couscous, cover, and set aside for 15 minutes. / Heat o</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -3706,38 +3518,37 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
+      <c r="I68" s="3" t="n"/>
       <c r="J68" s="3" t="n"/>
       <c r="K68" s="3" t="n"/>
-      <c r="L68" s="3" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>RCP2_35DC1259F6B0</t>
+          <t>RCP2_BBA025B49BA6</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Soft Shell Tacos</t>
+          <t>Pierogi</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>baked_good</t>
+          <t>main</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>flour 125.0 g（1 c. flour）; cornmeal 78.5 g（1/2 c. cornmeal）; salt 1.5 g（1/4 tsp. salt）; egg 50.0 g（1 egg）; water 474.0 g（2 c. water）</t>
+          <t>onion 110.0 g（1 medium onion）; butter 21.3 g（1 1/2 Tbsp. butter）; cheddar 340.2 g（3/4 lb. Cheddar cheese, grated）; milk 183.0 g（3/4 c. milk）; baking_powder 6.9 g（1 1/2 tsp. baking powder）; egg 100.0 g（2 eggs, well beaten）; potato 1065.0 g（5 medium potatoes, boiled and mashed）; flour 500.0 g（4 c. flour）</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Mix and drop on hot griddle. / Spread thin and cook until dry on top.</t>
+          <t>Saute onion in butter. / Add onion, cheese, butter, salt and pepper to mashed potatoes and mix well. / Sift flour, salt and baking powder into a bowl. / Add beaten eggs and milk. / Combine well and turn out onto floured board and knead for 10 minutes. Roll dough to form circle 1/4-inch thick. / Cut circle of dough with a 5-inch cutter. / Fill circles with tablespoon of potato filling. / Fold dough</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -3747,41 +3558,40 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>sauce</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
+          <t>one_bowl</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="n"/>
       <c r="J69" s="3" t="n"/>
       <c r="K69" s="3" t="n"/>
-      <c r="L69" s="3" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>RCP2_35DC1259F6B0</t>
+          <t>RCP2_BBA025B49BA6</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Soft Shell Tacos</t>
+          <t>Pierogi</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>baked_good</t>
+          <t>main</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>flour 125.0 g（1 c. flour）; cornmeal 78.5 g（1/2 c. cornmeal）; salt 1.5 g（1/4 tsp. salt）; egg 50.0 g（1 egg）; water 474.0 g（2 c. water）</t>
+          <t>onion 110.0 g（1 medium onion）; butter 21.3 g（1 1/2 Tbsp. butter）; cheddar 340.2 g（3/4 lb. Cheddar cheese, grated）; milk 183.0 g（3/4 c. milk）; baking_powder 6.9 g（1 1/2 tsp. baking powder）; egg 100.0 g（2 eggs, well beaten）; potato 1065.0 g（5 medium potatoes, boiled and mashed）; flour 500.0 g（4 c. flour）</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Mix and drop on hot griddle. / Spread thin and cook until dry on top.</t>
+          <t>Saute onion in butter. / Add onion, cheese, butter, salt and pepper to mashed potatoes and mix well. / Sift flour, salt and baking powder into a bowl. / Add beaten eggs and milk. / Combine well and turn out onto floured board and knead for 10 minutes. Roll dough to form circle 1/4-inch thick. / Cut circle of dough with a 5-inch cutter. / Fill circles with tablespoon of potato filling. / Fold dough</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -3791,26 +3601,25 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr"/>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="n"/>
       <c r="J70" s="3" t="n"/>
       <c r="K70" s="3" t="n"/>
-      <c r="L70" s="3" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>RCP2_4A7CC5A410F0</t>
+          <t>RCP2_C81AEF8EF1AC</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Plantains In Coconut Milk</t>
+          <t>Onion Creme Brulee</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3820,12 +3629,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>plantain 945.0 g（3 -4 plantains, sliced in rounds）; salt 1.5 g（1/4 teaspoon salt）; curry_powder 2.0 g（1 teaspoon curry powder）; cinnamon 1.3 g（1/2 teaspoon cinnamon）; cloves_spice 0.3 g（1/8 teaspoon clove）; coconut_milk 339.0 g（1 -2 cup coconut milk）</t>
+          <t>onion 220.0 g（2 large white onions）; egg_yolk 17.0 g（1 egg yolk）; sugar 50.0 g（50 g sugar）; cayenne 0.9 g（1/2 teaspoon cayenne pepper）; cream 50.3 g（50 ml heavy cream）; bacon 28.0 g（1 slice bacon (cooked crisp &amp; crumbled as garnish) (optional)）</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Combine all ingredients except coconut milk in a heavy saucepan. / Pour in 1 cup of coconut milk and simmer over low heat until plantain is very tender and milk is absorbed. / Add more coconut milk if necessary. Serve hot.</t>
+          <t>Preheat oven to 200°C Peel onion, leaving the root-end intact. Cut the non-root end top from the onion &amp; trim the root-end slightly to allow the onion shell to sit flat. / Remove as much of the inside pulp as poss w/o tearing the shell &amp; set the onion top + inside pulp aside. Bake shell in the oven for 10 minute Do not turn off the oven. / Rough chop the onion top + inside pulp. In a non-stick ski</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -3835,26 +3644,25 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>staple</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr"/>
+          <t>vegetable</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="n"/>
       <c r="J71" s="3" t="n"/>
       <c r="K71" s="3" t="n"/>
-      <c r="L71" s="3" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>RCP2_4A7CC5A410F0</t>
+          <t>RCP2_C81AEF8EF1AC</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Plantains In Coconut Milk</t>
+          <t>Onion Creme Brulee</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3864,12 +3672,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>plantain 945.0 g（3 -4 plantains, sliced in rounds）; salt 1.5 g（1/4 teaspoon salt）; curry_powder 2.0 g（1 teaspoon curry powder）; cinnamon 1.3 g（1/2 teaspoon cinnamon）; cloves_spice 0.3 g（1/8 teaspoon clove）; coconut_milk 339.0 g（1 -2 cup coconut milk）</t>
+          <t>onion 220.0 g（2 large white onions）; egg_yolk 17.0 g（1 egg yolk）; sugar 50.0 g（50 g sugar）; cayenne 0.9 g（1/2 teaspoon cayenne pepper）; cream 50.3 g（50 ml heavy cream）; bacon 28.0 g（1 slice bacon (cooked crisp &amp; crumbled as garnish) (optional)）</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Combine all ingredients except coconut milk in a heavy saucepan. / Pour in 1 cup of coconut milk and simmer over low heat until plantain is very tender and milk is absorbed. / Add more coconut milk if necessary. Serve hot.</t>
+          <t>Preheat oven to 200°C Peel onion, leaving the root-end intact. Cut the non-root end top from the onion &amp; trim the root-end slightly to allow the onion shell to sit flat. / Remove as much of the inside pulp as poss w/o tearing the shell &amp; set the onion top + inside pulp aside. Bake shell in the oven for 10 minute Do not turn off the oven. / Rough chop the onion top + inside pulp. In a non-stick ski</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -3879,41 +3687,40 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="n"/>
       <c r="J72" s="3" t="n"/>
       <c r="K72" s="3" t="n"/>
-      <c r="L72" s="3" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>RCP2_561E7EDAC82C</t>
+          <t>RCP2_CEEA9D67A7EE</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Cuban Black Beans</t>
+          <t>Basic Italian Cookies</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>baked_good</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>garlic 4.2 g（1 1/2 teaspoons chopped garlic）; olive_oil 9.0 g（2 teaspoons olive oil）; red_onion 40.0 g（1/4 cup chopped red onion）; bell_pepper 37.2 g（1/4 cup chopped red bell pepper）; carrot 32.0 g（1/4 cup chopped carrot）; jalapeno 28.0 g（2 jalapenos, seeded and chopped）; black_beans 344.0 g（2 cups cooked black beans (drained and rinsed if canned)）; coriander 1.4 g（1 1/2 teaspoons chopped fresh coriander）; lime_juice 30.2 g（2 tablespoons fresh lime juice）</t>
+          <t>flour 625.0 g（5 c. flour）; powdered_sugar 180.0 g（1 1/2 c. sifted confectioners sugar）; egg 150.0 g（3 eggs）; baking_powder 27.5 g（2 Tbsp. baking powder）; butter_or_margarine 227.0 g（1 c. margarine or butter）; vanilla 13.0 g（1 Tbsp. vanilla）</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>In a skillet, heat garlic and oil over moderate heat until garlic is fragrant. / Stir in onion, bell pepper, carrot and jalapeno. / Cook mixture, stirring occasionally, until vegetables are softened. / Stir in beans, coriander, lime juice, and salt and pepper to taste and cook, stirring till heated through. / Keep warm till serving time.</t>
+          <t>Blend sugar and baking powder with the flour with a wire whisk. / Put on a pastry board; make a well in the center of the flour mixture. / Break the eggs into the center and add the vanilla. / Knead the dough well for 5 minutes until it is smooth, adding a little flour if the dough seems too sticky and soft. Pinch off bits of dough about the size of a small apricot and form into desired shape (rin</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -3923,26 +3730,25 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>legume</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="n"/>
       <c r="J73" s="3" t="n"/>
       <c r="K73" s="3" t="n"/>
-      <c r="L73" s="3" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>RCP2_A31F833871D7</t>
+          <t>RCP2_DC882B3F674A</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Bread Dumplings</t>
+          <t>Banana Raita With Coconut</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3952,12 +3758,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>bread 87.0 g（3 slices white bread）; butter 28.4 g（2 Tbsp. butter）; flour 187.5 g（1 1/2 c. sifted flour）; salt 18.2 g（1 Tbsp. salt）; egg 50.0 g（1 beaten egg）; milk 183.0 g（3/4 c. milk）</t>
+          <t>banana 236.0 g（2 bananas, ripe medium sized peeled and cut into bite size pieces）; lemon_juice 5.2 g（1 teaspoon lemon juice）; yogurt 245.0 g（1 cup plain yogurt）; honey 21.0 g（1 tablespoon honey）; coconut 45.0 g（1/2 cup coconut, desiccated unsweetened）</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Dice and fry bread in butter until crisp. / Remove and place on paper towel. / In large bowl, mix flour and salt. / Mix egg and milk and stir into flour mixture. / Form into dumplings around bread cubes, using 3 to 4 cubes per dumpling. / Drop into boiling water, taking care that dumplings do not stick. / Cover and boil gently 15 to 20 minutes or until done. / Makes 4 servings.</t>
+          <t>Roast/dry fry coconut in a small pan or in a microwave, until a nice aroma rises and it changes colour to slightly brownish pink. You can toast the coconut in a microwave. Spread on a plate and cook on full for 3 (2+1) minutes. Keep aside. / Squeeze a little lemon juice over bananas, to keep them from discolouring. / Mix yogurt with honey and half the coconut. / Add bananas and stir lightly. / Gar</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -3967,26 +3773,25 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>staple</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr"/>
+          <t>sauce</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="n"/>
       <c r="J74" s="3" t="n"/>
       <c r="K74" s="3" t="n"/>
-      <c r="L74" s="3" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>RCP2_A31F833871D7</t>
+          <t>RCP2_DC882B3F674A</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Bread Dumplings</t>
+          <t>Banana Raita With Coconut</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3996,12 +3801,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>bread 87.0 g（3 slices white bread）; butter 28.4 g（2 Tbsp. butter）; flour 187.5 g（1 1/2 c. sifted flour）; salt 18.2 g（1 Tbsp. salt）; egg 50.0 g（1 beaten egg）; milk 183.0 g（3/4 c. milk）</t>
+          <t>banana 236.0 g（2 bananas, ripe medium sized peeled and cut into bite size pieces）; lemon_juice 5.2 g（1 teaspoon lemon juice）; yogurt 245.0 g（1 cup plain yogurt）; honey 21.0 g（1 tablespoon honey）; coconut 45.0 g（1/2 cup coconut, desiccated unsweetened）</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Dice and fry bread in butter until crisp. / Remove and place on paper towel. / In large bowl, mix flour and salt. / Mix egg and milk and stir into flour mixture. / Form into dumplings around bread cubes, using 3 to 4 cubes per dumpling. / Drop into boiling water, taking care that dumplings do not stick. / Cover and boil gently 15 to 20 minutes or until done. / Makes 4 servings.</t>
+          <t>Roast/dry fry coconut in a small pan or in a microwave, until a nice aroma rises and it changes colour to slightly brownish pink. You can toast the coconut in a microwave. Spread on a plate and cook on full for 3 (2+1) minutes. Keep aside. / Squeeze a little lemon juice over bananas, to keep them from discolouring. / Mix yogurt with honey and half the coconut. / Add bananas and stir lightly. / Gar</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -4011,26 +3816,25 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="n"/>
       <c r="J75" s="3" t="n"/>
       <c r="K75" s="3" t="n"/>
-      <c r="L75" s="3" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>RCP2_A660E279682A</t>
+          <t>RCP2_E20C08DE6172</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Easy Potato Dumplings</t>
+          <t>Polenta Gnocchi With Gorgonzola</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4040,12 +3844,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>instant_mashed_potato 60.0 g（1 cup instant instant potato flakes）; water 237.0 g（1 cup hot water）; salt 3.0 g（1/2 teaspoon salt）; egg 50.0 g（1 egg）; flour 125.0 g（1 cup all-purpose flour）; butter 56.8 g（1/4 cup melted butter）; breadcrumbs 27.0 g（1/4 cup breadcrumbs）</t>
+          <t>water 1422.0 g（6 c. water）; cornmeal 314.0 g（2 c. cornmeal）; salt 12.2 g（2 tsp. salt）; blue_cheese 226.8 g（1/2 lb. Gorgonzola cheese）</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Combine Potato Buds &amp; hot water. / Add remaining ingredients in given order, mix well. / Form into 2-inch balls with hands, flour hands occasionally so dough doesn't stick. / Cook in boiling salted water until they rise to the top. / Remove dumplings from water with a slotted spoon &amp; place in butter casserole dish. / Sprinkle with bread crumbs &amp; keep layering melted butter, dumplings &amp; crumbs. / C</t>
+          <t>In a large saucepan, slowly pour water into the cornmeal, stirring constantly, until free of lumps. Stir in rest of water and salt. Cook on medium-low heat for 20 to 30 minutes, stirring frequently, until thick and smooth. Be especially vigilant during last 10 minutes to prevent scorching. When polenta is done, spoon will stand up in the middle and mass will cling together and pull away from the s</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -4058,23 +3862,22 @@
           <t>staple</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
+      <c r="I76" s="3" t="n"/>
       <c r="J76" s="3" t="n"/>
       <c r="K76" s="3" t="n"/>
-      <c r="L76" s="3" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>RCP2_A660E279682A</t>
+          <t>RCP2_E20C08DE6172</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Easy Potato Dumplings</t>
+          <t>Polenta Gnocchi With Gorgonzola</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4084,12 +3887,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>instant_mashed_potato 60.0 g（1 cup instant instant potato flakes）; water 237.0 g（1 cup hot water）; salt 3.0 g（1/2 teaspoon salt）; egg 50.0 g（1 egg）; flour 125.0 g（1 cup all-purpose flour）; butter 56.8 g（1/4 cup melted butter）; breadcrumbs 27.0 g（1/4 cup breadcrumbs）</t>
+          <t>water 1422.0 g（6 c. water）; cornmeal 314.0 g（2 c. cornmeal）; salt 12.2 g（2 tsp. salt）; blue_cheese 226.8 g（1/2 lb. Gorgonzola cheese）</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Combine Potato Buds &amp; hot water. / Add remaining ingredients in given order, mix well. / Form into 2-inch balls with hands, flour hands occasionally so dough doesn't stick. / Cook in boiling salted water until they rise to the top. / Remove dumplings from water with a slotted spoon &amp; place in butter casserole dish. / Sprinkle with bread crumbs &amp; keep layering melted butter, dumplings &amp; crumbs. / C</t>
+          <t>In a large saucepan, slowly pour water into the cornmeal, stirring constantly, until free of lumps. Stir in rest of water and salt. Cook on medium-low heat for 20 to 30 minutes, stirring frequently, until thick and smooth. Be especially vigilant during last 10 minutes to prevent scorching. When polenta is done, spoon will stand up in the middle and mass will cling together and pull away from the s</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -4102,111 +3905,108 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
+      <c r="I77" s="3" t="n"/>
       <c r="J77" s="3" t="n"/>
       <c r="K77" s="3" t="n"/>
-      <c r="L77" s="3" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>RCP2_B8E67A023CFD</t>
+          <t>RCP2_E20C08DE6172</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Chtitha Batata (Algerian Potato Stew)</t>
+          <t>Polenta Gnocchi With Gorgonzola</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>side</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>garlic 12.0 g（4 cloves Garlic）; chili_pepper 45.0 g（1 small Red Chilli）; cumin 2.2 g（1 tsp Ground Cumin）; paprika 2.3 g（1 teaspoon Paprika）; black_pepper 1.1 g（1/2 teaspoon Black Pepper）; cayenne 0.9 g（1/2 teaspoon Cayenne Pepper）; salt 3.0 g（1/2 teaspoon Salt）; olive_oil 27.0 g（2 tablespoons Olive Oil）; potato 907.2 g（2 Lbs New Potatoes）; tomato_puree 15.6 g（1 tablespoon Tomato Puree）; water 500.9 g（Boiled Water）; salt 1.5 g（To taste Salt）</t>
+          <t>water 1422.0 g（6 c. water）; cornmeal 314.0 g（2 c. cornmeal）; salt 12.2 g（2 tsp. salt）; blue_cheese 226.8 g（1/2 lb. Gorgonzola cheese）</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Combine garlic, chile pepper, cumin, paprika, black pepper, cayenne, and salt in a mortar; grind with a pestle until it forms a paste. Add olive oil and mix dersa well. / Heat a large saucepan over medium heat and stir-fry dersa until fragrant, 2 to 4 minutes. Add potato halves and stir to combine with the dersa. Stir in tomato paste. Pour in enough water to just cover the potatoes and bring to a </t>
+          <t>In a large saucepan, slowly pour water into the cornmeal, stirring constantly, until free of lumps. Stir in rest of water and salt. Cook on medium-low heat for 20 to 30 minutes, stirring frequently, until thick and smooth. Be especially vigilant during last 10 minutes to prevent scorching. When polenta is done, spoon will stand up in the middle and mass will cling together and pull away from the s</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>meal_role</t>
+          <t>protein_sources</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>staple</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr"/>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="n"/>
       <c r="J78" s="3" t="n"/>
       <c r="K78" s="3" t="n"/>
-      <c r="L78" s="3" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>RCP2_B8E67A023CFD</t>
+          <t>RCP2_E8D667BA918A</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Chtitha Batata (Algerian Potato Stew)</t>
+          <t>Fake Feta</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>side</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>garlic 12.0 g（4 cloves Garlic）; chili_pepper 45.0 g（1 small Red Chilli）; cumin 2.2 g（1 tsp Ground Cumin）; paprika 2.3 g（1 teaspoon Paprika）; black_pepper 1.1 g（1/2 teaspoon Black Pepper）; cayenne 0.9 g（1/2 teaspoon Cayenne Pepper）; salt 3.0 g（1/2 teaspoon Salt）; olive_oil 27.0 g（2 tablespoons Olive Oil）; potato 907.2 g（2 Lbs New Potatoes）; tomato_puree 15.6 g（1 tablespoon Tomato Puree）; water 500.9 g（Boiled Water）; salt 1.5 g（To taste Salt）</t>
+          <t>olive_oil 54.0 g（1/4 cup olive oil）; water 59.2 g（1/4 cup water）; red_wine_vinegar 119.5 g（1/2 cup red wine vinegar）; salt 12.2 g（2 teaspoons salt）; basil 0.5 g（1 teaspoon dried basil）; oregano 0.9 g（1/2 teaspoon oregano）; basil 0.2 g（1/2 teaspoon basil）; tofu 453.6 g（1 lb firm tofu）</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Combine garlic, chile pepper, cumin, paprika, black pepper, cayenne, and salt in a mortar; grind with a pestle until it forms a paste. Add olive oil and mix dersa well. / Heat a large saucepan over medium heat and stir-fry dersa until fragrant, 2 to 4 minutes. Add potato halves and stir to combine with the dersa. Stir in tomato paste. Pour in enough water to just cover the potatoes and bring to a </t>
+          <t>In a large bowl, mix together first 7 ingredients. / Marinate the tofu in the mixture for at least an hour. / Enjoy in your favorite recipes.</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>contains_staple</t>
+          <t>meal_role</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr"/>
+          <t>sauce</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="n"/>
       <c r="J79" s="3" t="n"/>
       <c r="K79" s="3" t="n"/>
-      <c r="L79" s="3" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>RCP2_C25D9C4D878B</t>
+          <t>RCP2_E8D667BA918A</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire Pudding</t>
+          <t>Fake Feta</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4216,305 +4016,298 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>egg 100.0 g（2 eggs）; milk 488.0 g（2 c. milk）; flour 125.0 g（1 c. all purpose flour）</t>
+          <t>olive_oil 54.0 g（1/4 cup olive oil）; water 59.2 g（1/4 cup water）; red_wine_vinegar 119.5 g（1/2 cup red wine vinegar）; salt 12.2 g（2 teaspoons salt）; basil 0.5 g（1 teaspoon dried basil）; oregano 0.9 g（1/2 teaspoon oregano）; basil 0.2 g（1/2 teaspoon basil）; tofu 453.6 g（1 lb firm tofu）</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Preheat oven to 350°. Combine eggs and milk in bowl. Stir in flour; mix well. Pour into greased 8 inch square pan. Bake for 30 minutes. Yield: 4 to 6 serving.</t>
+          <t>In a large bowl, mix together first 7 ingredients. / Marinate the tofu in the mixture for at least an hour. / Enjoy in your favorite recipes.</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>meal_role</t>
+          <t>contains_staple</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>staple</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="n"/>
       <c r="J80" s="3" t="n"/>
       <c r="K80" s="3" t="n"/>
-      <c r="L80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>RCP2_C25D9C4D878B</t>
+          <t>RCP2_EAAD839F9258</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire Pudding</t>
+          <t>Mushroom-Barley Soup</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>soup</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>egg 100.0 g（2 eggs）; milk 488.0 g（2 c. milk）; flour 125.0 g（1 c. all purpose flour）</t>
+          <t>onion 99.2 g（3 1/2 oz. onions, chopped）; celery 99.2 g（3 1/2 oz. celery, chopped）; garlic 3.0 g（1 clove garlic, minced）; butter 56.8 g（4 Tbsp. butter）; barley 70.9 g（2 1/2 oz. barley）; chicken_broth 1892.8 g（2 qt. chicken stock）; mushroom 368.5 g（13 oz. fresh mushrooms, sauteed in 1/4 c. butter）</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Preheat oven to 350°. Combine eggs and milk in bowl. Stir in flour; mix well. Pour into greased 8 inch square pan. Bake for 30 minutes. Yield: 4 to 6 serving.</t>
+          <t>Saute onions, celery and garlic in butter until tender. / Add dry barley and saute 10 more minutes until barley gets thick. Add chicken stock and mushrooms. Boil and simmer until barley is tender, about 1/2 hour to 45 minutes. Serves 6.</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>contains_staple</t>
+          <t>meal_role</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr"/>
+          <t>soup</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="n"/>
       <c r="J81" s="3" t="n"/>
       <c r="K81" s="3" t="n"/>
-      <c r="L81" s="3" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>RCP2_C8B759477F8B</t>
+          <t>RCP2_EAAD839F9258</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Gözleme (Turkish Flatbread)</t>
+          <t>Mushroom-Barley Soup</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>soup</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>flour 656.2 g（5¼ cups (600 grams) all-purpose flour）; salt 15.2 g（2½ teaspoons (15 grams) salt）; yeast 6.3 g（2 teaspoons (7 grams) dry yeast）; sugar 4.2 g（1 teaspoon (4 grams) white granulated sugar）; water 296.2 g（1¼ cups (300 grams) water）; vegetable_oil 109.0 g（½ cup (100 grams) oil）; butter 75.7 g（⅓ cup (65 grams) butter）</t>
+          <t>onion 99.2 g（3 1/2 oz. onions, chopped）; celery 99.2 g（3 1/2 oz. celery, chopped）; garlic 3.0 g（1 clove garlic, minced）; butter 56.8 g（4 Tbsp. butter）; barley 70.9 g（2 1/2 oz. barley）; chicken_broth 1892.8 g（2 qt. chicken stock）; mushroom 368.5 g（13 oz. fresh mushrooms, sauteed in 1/4 c. butter）</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Sift flour in a large bowl, reserving 1 cup of flour. / Sprinkle with salt and mix. Make a well in the centre. / Combine yeast and sugar in a small bowl. Stir in ¼ cup warm water. / Pour the liquid into the well in the centre of the flour. / Cover yeast with some flour. Let stand for 10 minutes to rise. / Stir in remaining liquid, blending thoroughly. Knead for 5 minutes to form a medium-soft doug</t>
+          <t>Saute onions, celery and garlic in butter until tender. / Add dry barley and saute 10 more minutes until barley gets thick. Add chicken stock and mushrooms. Boil and simmer until barley is tender, about 1/2 hour to 45 minutes. Serves 6.</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>meal_role</t>
+          <t>contains_staple</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>staple</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="n"/>
       <c r="J82" s="3" t="n"/>
       <c r="K82" s="3" t="n"/>
-      <c r="L82" s="3" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>RCP2_C8B759477F8B</t>
+          <t>RCP2_ED8C37EACE4D</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Gözleme (Turkish Flatbread)</t>
+          <t>Mock Feta Cheese ( Vegan Substitute )</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>side</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>flour 656.2 g（5¼ cups (600 grams) all-purpose flour）; salt 15.2 g（2½ teaspoons (15 grams) salt）; yeast 6.3 g（2 teaspoons (7 grams) dry yeast）; sugar 4.2 g（1 teaspoon (4 grams) white granulated sugar）; water 296.2 g（1¼ cups (300 grams) water）; vegetable_oil 109.0 g（½ cup (100 grams) oil）; butter 75.7 g（⅓ cup (65 grams) butter）</t>
+          <t>olive_oil 54.0 g（1/4 cup olive oil）; water 59.2 g（1/4 cup water）; red_wine_vinegar 119.5 g（1/2 cup red wine vinegar）; salt 12.2 g（2 teaspoons salt）; basil 1.5 g（1 tablespoon dried basil）; oregano 0.9 g（1/2 teaspoon dried oregano）; black_pepper 1.1 g（1/2 teaspoon pepper）; tofu 453.6 g（1 lb firm tofu, herb flavored, cubed or crumbled）</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Sift flour in a large bowl, reserving 1 cup of flour. / Sprinkle with salt and mix. Make a well in the centre. / Combine yeast and sugar in a small bowl. Stir in ¼ cup warm water. / Pour the liquid into the well in the centre of the flour. / Cover yeast with some flour. Let stand for 10 minutes to rise. / Stir in remaining liquid, blending thoroughly. Knead for 5 minutes to form a medium-soft doug</t>
+          <t>Place everything but the tofu in the bowl and whisk together. / Add tofu, stir, and let sit for at least an hour.</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>contains_staple</t>
+          <t>meal_role</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr"/>
+          <t>sauce</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="n"/>
       <c r="J83" s="3" t="n"/>
       <c r="K83" s="3" t="n"/>
-      <c r="L83" s="3" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>RCP2_D1A78AFA0C85</t>
+          <t>RCP2_ED8C37EACE4D</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Teenage Sloppy Joes</t>
+          <t>Mock Feta Cheese ( Vegan Substitute )</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>side</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>beef 907.2 g（2 lb. ground beef）; bell_pepper 149.0 g（1 c. green peppers）; onion 160.0 g（1 c. chopped onion）; bbq_sauce 520.0 g（2 c. barbecue sauce）; water 474.0 g（2 c. water）; oats 81.0 g（1 c. oats）; flour 15.6 g（2 Tbsp. flour）; salt 6.1 g（1 tsp. salt）</t>
+          <t>olive_oil 54.0 g（1/4 cup olive oil）; water 59.2 g（1/4 cup water）; red_wine_vinegar 119.5 g（1/2 cup red wine vinegar）; salt 12.2 g（2 teaspoons salt）; basil 1.5 g（1 tablespoon dried basil）; oregano 0.9 g（1/2 teaspoon dried oregano）; black_pepper 1.1 g（1/2 teaspoon pepper）; tofu 453.6 g（1 lb firm tofu, herb flavored, cubed or crumbled）</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Combine beef, green peppers and onion in skillet until brown. Add mixed oats, flour, salt and water with barbecue sauce and cook until done. / This recipe will serve 6 people.</t>
+          <t>Place everything but the tofu in the bowl and whisk together. / Add tofu, stir, and let sit for at least an hour.</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>meal_role</t>
+          <t>contains_staple</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>protein_main</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="n"/>
       <c r="J84" s="3" t="n"/>
       <c r="K84" s="3" t="n"/>
-      <c r="L84" s="3" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>RCP2_D1A78AFA0C85</t>
+          <t>RCP2_F0A2E3140892</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Teenage Sloppy Joes</t>
+          <t>Hearty French Onion Soup</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>soup</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>beef 907.2 g（2 lb. ground beef）; bell_pepper 149.0 g（1 c. green peppers）; onion 160.0 g（1 c. chopped onion）; bbq_sauce 520.0 g（2 c. barbecue sauce）; water 474.0 g（2 c. water）; oats 81.0 g（1 c. oats）; flour 15.6 g（2 Tbsp. flour）; salt 6.1 g（1 tsp. salt）</t>
+          <t>butter 56.8 g（1/4 c. butter）; onion 550.0 g（5 medium yellow onions, thinly sliced）; sugar 0.5 g（1/8 tsp. sugar）; flour 15.6 g（2 Tbsp. flour）; beef_broth 1200.0 g（5 c. low sodium beef broth）; thyme 0.3 g（1/2 tsp. thyme, crumbled）; bay_leaf 0.2 g（1 bay leaf）; black_pepper 0.6 g（1/4 tsp. pepper）; bread 232.0 g（8 (1/2-inch) slices French bread, toasted）; swiss_cheese 108.0 g（1 c. shredded Swiss cheese）; parmesan 25.0 g（1/4 c. Parmesan cheese）</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Combine beef, green peppers and onion in skillet until brown. Add mixed oats, flour, salt and water with barbecue sauce and cook until done. / This recipe will serve 6 people.</t>
+          <t xml:space="preserve">Melt butter in large saucepan over medium heat. / Add onions. Cook for 10 to 15 minutes or until golden, stirring gently. / Stir in sugar and flour. / Cook for 3 minutes longer, stirring constantly. / Add broth, thyme, bay leaf and pepper; mix well. Bring to a boil over medium-high heat, stirring constantly. / Boil for 6 minutes, stirring constantly; reduce heat. / Simmer, loosely covered, for 30 </t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>contains_staple</t>
+          <t>meal_role</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr"/>
+          <t>soup</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="n"/>
       <c r="J85" s="3" t="n"/>
       <c r="K85" s="3" t="n"/>
-      <c r="L85" s="3" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>RCP2_F9AC64939A2C</t>
+          <t>RCP2_F0A2E3140892</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Welsh Rarebit</t>
+          <t>Hearty French Onion Soup</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>soup</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>butter 21.3 g（1 1/2 Tbsp. butter）; flour 11.7 g（1 1/2 Tbsp. flour）; milk 366.0 g（1 1/2 c. milk）; cheddar 113.0 g（1 c. grated Cheddar cheese）; salt 3.0 g（1/2 tsp. salt）; mustard 2.6 g（1/2 tsp. mustard）; paprika 0.3 g（1/8 tsp. paprika）</t>
+          <t>butter 56.8 g（1/4 c. butter）; onion 550.0 g（5 medium yellow onions, thinly sliced）; sugar 0.5 g（1/8 tsp. sugar）; flour 15.6 g（2 Tbsp. flour）; beef_broth 1200.0 g（5 c. low sodium beef broth）; thyme 0.3 g（1/2 tsp. thyme, crumbled）; bay_leaf 0.2 g（1 bay leaf）; black_pepper 0.6 g（1/4 tsp. pepper）; bread 232.0 g（8 (1/2-inch) slices French bread, toasted）; swiss_cheese 108.0 g（1 c. shredded Swiss cheese）; parmesan 25.0 g（1/4 c. Parmesan cheese）</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Make white sauce of butter, flour and milk. / Add cheese and stir over low heat until cheese is melted. / Add seasonings. / Serve hot over buttered toast or crackers.</t>
+          <t xml:space="preserve">Melt butter in large saucepan over medium heat. / Add onions. Cook for 10 to 15 minutes or until golden, stirring gently. / Stir in sugar and flour. / Cook for 3 minutes longer, stirring constantly. / Add broth, thyme, bay leaf and pepper; mix well. Bring to a boil over medium-high heat, stirring constantly. / Boil for 6 minutes, stirring constantly; reduce heat. / Simmer, loosely covered, for 30 </t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>protein_sources</t>
+          <t>contains_staple</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="n"/>
       <c r="J86" s="3" t="n"/>
       <c r="K86" s="3" t="n"/>
-      <c r="L86" s="3" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>RCP2_FB5F31874C8A</t>
+          <t>RCP2_F918B184F959</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Fresh Ramen Egg Noodles From Scratch</t>
+          <t>Spaetzle</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4524,12 +4317,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>flour 62.5 g（1/2 cup unbleached all-purpose flour）; semolina_flour 83.5 g（1/2 cup semolina flour）; salt 1.5 g（1/4 teaspoon fine sea salt）; garlic_powder 0.7 g（1/4 teaspoon garlic powder）; egg 50.0 g（1 egg, beaten）; sesame_oil 13.6 g（1 tablespoon sesame oil）; water 118.5 g（1/2 cup water, or as needed）</t>
+          <t>flour 312.5 g（2 1/2 cups flour）; egg 150.0 g（3 eggs）; salt 6.1 g（1 tsp salt）; milk 122.0 g（1/2 cup milk）; water 118.5 g（1/2 cup water）</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Place all-purpose flour, semolina flour, sea salt, and garlic powder in a food processor. Pulse to blend well. Reduce speed to low. Add egg and sesame oil through the feeder. / Increase speed to high. Add 1 tablespoon water, reduce speed to low, and blend. Set speed back to high; continue adding water 1 tablespoon at a time and blending on low until dough forms into a ball. Stop adding water immed</t>
+          <t>Mix all ingredients very well, with a strong, upward, whipping motion. / Put a batch of the dough on a small cutting board and scrape it off the board into a pot of boiling salted water, forming small button - to thin egg-noodle size noodles. Noodles will float to the top of the water when they are cooked. Remove with a strainer or slotted spoon.</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -4542,23 +4335,22 @@
           <t>staple</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
+      <c r="I87" s="3" t="n"/>
       <c r="J87" s="3" t="n"/>
       <c r="K87" s="3" t="n"/>
-      <c r="L87" s="3" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>RCP2_FB5F31874C8A</t>
+          <t>RCP2_F918B184F959</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Fresh Ramen Egg Noodles From Scratch</t>
+          <t>Spaetzle</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -4568,12 +4360,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>flour 62.5 g（1/2 cup unbleached all-purpose flour）; semolina_flour 83.5 g（1/2 cup semolina flour）; salt 1.5 g（1/4 teaspoon fine sea salt）; garlic_powder 0.7 g（1/4 teaspoon garlic powder）; egg 50.0 g（1 egg, beaten）; sesame_oil 13.6 g（1 tablespoon sesame oil）; water 118.5 g（1/2 cup water, or as needed）</t>
+          <t>flour 312.5 g（2 1/2 cups flour）; egg 150.0 g（3 eggs）; salt 6.1 g（1 tsp salt）; milk 122.0 g（1/2 cup milk）; water 118.5 g（1/2 cup water）</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Place all-purpose flour, semolina flour, sea salt, and garlic powder in a food processor. Pulse to blend well. Reduce speed to low. Add egg and sesame oil through the feeder. / Increase speed to high. Add 1 tablespoon water, reduce speed to low, and blend. Set speed back to high; continue adding water 1 tablespoon at a time and blending on low until dough forms into a ball. Stop adding water immed</t>
+          <t>Mix all ingredients very well, with a strong, upward, whipping motion. / Put a batch of the dough on a small cutting board and scrape it off the board into a pot of boiling salted water, forming small button - to thin egg-noodle size noodles. Noodles will float to the top of the water when they are cooked. Remove with a strainer or slotted spoon.</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -4586,10 +4378,224 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
+      <c r="I88" s="3" t="n"/>
       <c r="J88" s="3" t="n"/>
       <c r="K88" s="3" t="n"/>
-      <c r="L88" s="3" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_F918B184F959</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Spaetzle</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>flour 312.5 g（2 1/2 cups flour）; egg 150.0 g（3 eggs）; salt 6.1 g（1 tsp salt）; milk 122.0 g（1/2 cup milk）; water 118.5 g（1/2 cup water）</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Mix all ingredients very well, with a strong, upward, whipping motion. / Put a batch of the dough on a small cutting board and scrape it off the board into a pot of boiling salted water, forming small button - to thin egg-noodle size noodles. Noodles will float to the top of the water when they are cooked. Remove with a strainer or slotted spoon.</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>protein_sources</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="n"/>
+      <c r="J89" s="3" t="n"/>
+      <c r="K89" s="3" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_F9AC64939A2C</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Welsh Rarebit</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>butter 21.3 g（1 1/2 Tbsp. butter）; flour 11.7 g（1 1/2 Tbsp. flour）; milk 366.0 g（1 1/2 c. milk）; cheddar 113.0 g（1 c. grated Cheddar cheese）; salt 3.0 g（1/2 tsp. salt）; mustard 2.6 g（1/2 tsp. mustard）; paprika 0.3 g（1/8 tsp. paprika）</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Make white sauce of butter, flour and milk. / Add cheese and stir over low heat until cheese is melted. / Add seasonings. / Serve hot over buttered toast or crackers.</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>meal_role</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>sauce</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="n"/>
+      <c r="J90" s="3" t="n"/>
+      <c r="K90" s="3" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_F9AC64939A2C</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Welsh Rarebit</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>butter 21.3 g（1 1/2 Tbsp. butter）; flour 11.7 g（1 1/2 Tbsp. flour）; milk 366.0 g（1 1/2 c. milk）; cheddar 113.0 g（1 c. grated Cheddar cheese）; salt 3.0 g（1/2 tsp. salt）; mustard 2.6 g（1/2 tsp. mustard）; paprika 0.3 g（1/8 tsp. paprika）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Make white sauce of butter, flour and milk. / Add cheese and stir over low heat until cheese is melted. / Add seasonings. / Serve hot over buttered toast or crackers.</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>contains_staple</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="n"/>
+      <c r="J91" s="3" t="n"/>
+      <c r="K91" s="3" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_FF3C50B5519E</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Vietnamese "Banh Mi" Chicken Burger</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>cucumber 301.0 g（1 small cucumber, thinly sliced）; carrot 61.0 g（1 medium carrot, peeled and sliced into ribbons）; radish 51.0 g（3 radishes, thinly sliced）; vinegar 240.0 g（1 cup white vinegar）; salt 15.2 g（2 1/2 teaspoon salt, divided）; sugar 4.2 g（1 teaspoon sugar）; tofu 170.1 g（6 ounces firm tofu）; egg 50.0 g（1 egg）; green_onion 25.0 g（1/4 cup scallions, chopped）; black_pepper 1.1 g（1/2 teaspoon black pepper, divided）; chicken 567.0 g（1 1/4 pounds ground chicken）; olive_oil 13.5 g（1 tablespoon olive oil）; sesame_oil 9.1 g（2 teaspoons sesame oil）; mushroom 226.8 g（1/2 pound shiitake mushrooms）; soy_sauce 10.6 g（2 teaspoons soy sauce）; cider_vinegar 7.5 g（1 1/2 teaspoon apple cider vinegar）; cumin 0.6 g（1/4 teaspoon ground cumin）; brown_sugar 0.6 g（1/8 teaspoon brown sugar）; bean_sprouts 104.0 g（1 cup bean sprouts）; cilantro 40.0 g（1 bunch cilantro, chopped）; hamburger_bun 172.0 g（4 whole-wheat hamburger buns）</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>In a glass bowl, combine cucumber, carrot and radishes. In a small pot, bring white vinegar, 1 1/2 teaspoon salt, sugar and 1 cup water to a boil; pour over vegetables and refrigerate until pickled, 1 hour. Heat oven to 400°F. In a food processor, pulse tofu, egg, scallions, 1/4 teaspoon pepper and remaining 1 teaspoon salt until combined, 30 seconds. In a bowl, fold tofu mixture into chicken; for</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>meal_role</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>one_bowl</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="n"/>
+      <c r="J92" s="3" t="n"/>
+      <c r="K92" s="3" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>RCP2_FF3C50B5519E</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Vietnamese "Banh Mi" Chicken Burger</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>cucumber 301.0 g（1 small cucumber, thinly sliced）; carrot 61.0 g（1 medium carrot, peeled and sliced into ribbons）; radish 51.0 g（3 radishes, thinly sliced）; vinegar 240.0 g（1 cup white vinegar）; salt 15.2 g（2 1/2 teaspoon salt, divided）; sugar 4.2 g（1 teaspoon sugar）; tofu 170.1 g（6 ounces firm tofu）; egg 50.0 g（1 egg）; green_onion 25.0 g（1/4 cup scallions, chopped）; black_pepper 1.1 g（1/2 teaspoon black pepper, divided）; chicken 567.0 g（1 1/4 pounds ground chicken）; olive_oil 13.5 g（1 tablespoon olive oil）; sesame_oil 9.1 g（2 teaspoons sesame oil）; mushroom 226.8 g（1/2 pound shiitake mushrooms）; soy_sauce 10.6 g（2 teaspoons soy sauce）; cider_vinegar 7.5 g（1 1/2 teaspoon apple cider vinegar）; cumin 0.6 g（1/4 teaspoon ground cumin）; brown_sugar 0.6 g（1/8 teaspoon brown sugar）; bean_sprouts 104.0 g（1 cup bean sprouts）; cilantro 40.0 g（1 bunch cilantro, chopped）; hamburger_bun 172.0 g（4 whole-wheat hamburger buns）</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>In a glass bowl, combine cucumber, carrot and radishes. In a small pot, bring white vinegar, 1 1/2 teaspoon salt, sugar and 1 cup water to a boil; pour over vegetables and refrigerate until pickled, 1 hour. Heat oven to 400°F. In a food processor, pulse tofu, egg, scallions, 1/4 teaspoon pepper and remaining 1 teaspoon salt until combined, 30 seconds. In a bowl, fold tofu mixture into chicken; for</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>contains_staple</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="n"/>
+      <c r="J93" s="3" t="n"/>
+      <c r="K93" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
